--- a/output/version3/test/15-10/MARL/CTDE/RL-RL with EP (+comm)/(RL+RL) test results.xlsx
+++ b/output/version3/test/15-10/MARL/CTDE/RL-RL with EP (+comm)/(RL+RL) test results.xlsx
@@ -471,37 +471,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>635</v>
+        <v>620</v>
       </c>
       <c r="C2" t="n">
-        <v>591</v>
+        <v>677</v>
       </c>
       <c r="D2" t="n">
-        <v>606</v>
+        <v>630</v>
       </c>
       <c r="E2" t="n">
-        <v>607</v>
+        <v>626</v>
       </c>
       <c r="F2" t="n">
-        <v>564</v>
+        <v>611</v>
       </c>
       <c r="G2" t="n">
-        <v>569</v>
+        <v>602</v>
       </c>
       <c r="H2" t="n">
-        <v>521</v>
+        <v>563</v>
       </c>
       <c r="I2" t="n">
+        <v>620</v>
+      </c>
+      <c r="J2" t="n">
+        <v>686</v>
+      </c>
+      <c r="K2" t="n">
         <v>654</v>
       </c>
-      <c r="J2" t="n">
-        <v>591</v>
-      </c>
-      <c r="K2" t="n">
-        <v>650</v>
-      </c>
       <c r="L2" t="n">
-        <v>598.8</v>
+        <v>628.9</v>
       </c>
     </row>
     <row r="3">
@@ -509,37 +509,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>661</v>
+        <v>602</v>
       </c>
       <c r="C3" t="n">
-        <v>647</v>
+        <v>627</v>
       </c>
       <c r="D3" t="n">
-        <v>598</v>
+        <v>691</v>
       </c>
       <c r="E3" t="n">
+        <v>628</v>
+      </c>
+      <c r="F3" t="n">
+        <v>572</v>
+      </c>
+      <c r="G3" t="n">
+        <v>607</v>
+      </c>
+      <c r="H3" t="n">
+        <v>587</v>
+      </c>
+      <c r="I3" t="n">
+        <v>590</v>
+      </c>
+      <c r="J3" t="n">
         <v>620</v>
       </c>
-      <c r="F3" t="n">
-        <v>648</v>
-      </c>
-      <c r="G3" t="n">
-        <v>628</v>
-      </c>
-      <c r="H3" t="n">
-        <v>776</v>
-      </c>
-      <c r="I3" t="n">
-        <v>696</v>
-      </c>
-      <c r="J3" t="n">
-        <v>660</v>
-      </c>
       <c r="K3" t="n">
-        <v>618</v>
+        <v>580</v>
       </c>
       <c r="L3" t="n">
-        <v>655.2</v>
+        <v>610.4</v>
       </c>
     </row>
     <row r="4">
@@ -547,37 +547,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>637</v>
+        <v>618</v>
       </c>
       <c r="C4" t="n">
-        <v>606</v>
+        <v>620</v>
       </c>
       <c r="D4" t="n">
-        <v>615</v>
+        <v>595</v>
       </c>
       <c r="E4" t="n">
-        <v>625</v>
+        <v>670</v>
       </c>
       <c r="F4" t="n">
-        <v>682</v>
+        <v>649</v>
       </c>
       <c r="G4" t="n">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="H4" t="n">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="I4" t="n">
-        <v>684</v>
+        <v>593</v>
       </c>
       <c r="J4" t="n">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="K4" t="n">
-        <v>571</v>
+        <v>631</v>
       </c>
       <c r="L4" t="n">
-        <v>621</v>
+        <v>615.7</v>
       </c>
     </row>
     <row r="5">
@@ -585,37 +585,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>734</v>
+        <v>696</v>
       </c>
       <c r="C5" t="n">
-        <v>606</v>
+        <v>722</v>
       </c>
       <c r="D5" t="n">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="E5" t="n">
-        <v>669</v>
+        <v>707</v>
       </c>
       <c r="F5" t="n">
-        <v>630</v>
+        <v>685</v>
       </c>
       <c r="G5" t="n">
-        <v>632</v>
+        <v>682</v>
       </c>
       <c r="H5" t="n">
-        <v>672</v>
+        <v>767</v>
       </c>
       <c r="I5" t="n">
-        <v>670</v>
+        <v>818</v>
       </c>
       <c r="J5" t="n">
-        <v>674</v>
+        <v>623</v>
       </c>
       <c r="K5" t="n">
-        <v>620</v>
+        <v>723</v>
       </c>
       <c r="L5" t="n">
-        <v>658.4</v>
+        <v>710.3</v>
       </c>
     </row>
     <row r="6">
@@ -623,37 +623,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>639</v>
+        <v>647</v>
       </c>
       <c r="C6" t="n">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="D6" t="n">
-        <v>585</v>
+        <v>596</v>
       </c>
       <c r="E6" t="n">
-        <v>592</v>
+        <v>579</v>
       </c>
       <c r="F6" t="n">
-        <v>611</v>
+        <v>606</v>
       </c>
       <c r="G6" t="n">
-        <v>598</v>
+        <v>645</v>
       </c>
       <c r="H6" t="n">
-        <v>650</v>
+        <v>596</v>
       </c>
       <c r="I6" t="n">
-        <v>600</v>
+        <v>620</v>
       </c>
       <c r="J6" t="n">
-        <v>615</v>
+        <v>608</v>
       </c>
       <c r="K6" t="n">
-        <v>607</v>
+        <v>652</v>
       </c>
       <c r="L6" t="n">
-        <v>609.5</v>
+        <v>614.6</v>
       </c>
     </row>
     <row r="7">
@@ -661,37 +661,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>593</v>
+        <v>641</v>
       </c>
       <c r="C7" t="n">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="D7" t="n">
-        <v>570</v>
+        <v>666</v>
       </c>
       <c r="E7" t="n">
-        <v>661</v>
+        <v>638</v>
       </c>
       <c r="F7" t="n">
-        <v>625</v>
+        <v>583</v>
       </c>
       <c r="G7" t="n">
-        <v>658</v>
+        <v>621</v>
       </c>
       <c r="H7" t="n">
-        <v>635</v>
+        <v>614</v>
       </c>
       <c r="I7" t="n">
-        <v>660</v>
+        <v>647</v>
       </c>
       <c r="J7" t="n">
-        <v>595</v>
+        <v>752</v>
       </c>
       <c r="K7" t="n">
-        <v>596</v>
+        <v>582</v>
       </c>
       <c r="L7" t="n">
-        <v>621.6</v>
+        <v>636.3</v>
       </c>
     </row>
     <row r="8">
@@ -699,37 +699,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>673</v>
+        <v>558</v>
       </c>
       <c r="C8" t="n">
-        <v>569</v>
+        <v>593</v>
       </c>
       <c r="D8" t="n">
-        <v>661</v>
+        <v>629</v>
       </c>
       <c r="E8" t="n">
-        <v>692</v>
+        <v>656</v>
       </c>
       <c r="F8" t="n">
-        <v>619</v>
+        <v>589</v>
       </c>
       <c r="G8" t="n">
-        <v>637</v>
+        <v>558</v>
       </c>
       <c r="H8" t="n">
-        <v>583</v>
+        <v>561</v>
       </c>
       <c r="I8" t="n">
-        <v>584</v>
+        <v>601</v>
       </c>
       <c r="J8" t="n">
-        <v>554</v>
+        <v>594</v>
       </c>
       <c r="K8" t="n">
-        <v>622</v>
+        <v>600</v>
       </c>
       <c r="L8" t="n">
-        <v>619.4</v>
+        <v>593.9</v>
       </c>
     </row>
     <row r="9">
@@ -737,37 +737,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>599</v>
+        <v>575</v>
       </c>
       <c r="C9" t="n">
-        <v>616</v>
+        <v>712</v>
       </c>
       <c r="D9" t="n">
-        <v>572</v>
+        <v>608</v>
       </c>
       <c r="E9" t="n">
-        <v>640</v>
+        <v>524</v>
       </c>
       <c r="F9" t="n">
-        <v>626</v>
+        <v>742</v>
       </c>
       <c r="G9" t="n">
-        <v>628</v>
+        <v>641</v>
       </c>
       <c r="H9" t="n">
-        <v>583</v>
+        <v>635</v>
       </c>
       <c r="I9" t="n">
-        <v>682</v>
+        <v>527</v>
       </c>
       <c r="J9" t="n">
-        <v>624</v>
+        <v>636</v>
       </c>
       <c r="K9" t="n">
-        <v>582</v>
+        <v>625</v>
       </c>
       <c r="L9" t="n">
-        <v>615.2</v>
+        <v>622.5</v>
       </c>
     </row>
     <row r="10">
@@ -775,37 +775,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>705</v>
+        <v>694</v>
       </c>
       <c r="C10" t="n">
+        <v>692</v>
+      </c>
+      <c r="D10" t="n">
+        <v>712</v>
+      </c>
+      <c r="E10" t="n">
+        <v>764</v>
+      </c>
+      <c r="F10" t="n">
+        <v>785</v>
+      </c>
+      <c r="G10" t="n">
+        <v>698</v>
+      </c>
+      <c r="H10" t="n">
+        <v>724</v>
+      </c>
+      <c r="I10" t="n">
+        <v>712</v>
+      </c>
+      <c r="J10" t="n">
+        <v>712</v>
+      </c>
+      <c r="K10" t="n">
         <v>699</v>
       </c>
-      <c r="D10" t="n">
-        <v>707</v>
-      </c>
-      <c r="E10" t="n">
-        <v>703</v>
-      </c>
-      <c r="F10" t="n">
-        <v>716</v>
-      </c>
-      <c r="G10" t="n">
-        <v>762</v>
-      </c>
-      <c r="H10" t="n">
-        <v>756</v>
-      </c>
-      <c r="I10" t="n">
-        <v>667</v>
-      </c>
-      <c r="J10" t="n">
-        <v>730</v>
-      </c>
-      <c r="K10" t="n">
-        <v>850</v>
-      </c>
       <c r="L10" t="n">
-        <v>729.5</v>
+        <v>719.2</v>
       </c>
     </row>
     <row r="11">
@@ -813,37 +813,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>560</v>
+        <v>657</v>
       </c>
       <c r="C11" t="n">
-        <v>674</v>
+        <v>568</v>
       </c>
       <c r="D11" t="n">
-        <v>648</v>
+        <v>653</v>
       </c>
       <c r="E11" t="n">
-        <v>649</v>
+        <v>762</v>
       </c>
       <c r="F11" t="n">
-        <v>631</v>
+        <v>754</v>
       </c>
       <c r="G11" t="n">
-        <v>618</v>
+        <v>629</v>
       </c>
       <c r="H11" t="n">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="I11" t="n">
-        <v>695</v>
+        <v>663</v>
       </c>
       <c r="J11" t="n">
-        <v>620</v>
+        <v>598</v>
       </c>
       <c r="K11" t="n">
-        <v>625</v>
+        <v>687</v>
       </c>
       <c r="L11" t="n">
-        <v>637</v>
+        <v>661.7</v>
       </c>
     </row>
     <row r="12">
@@ -851,37 +851,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>637</v>
+        <v>660</v>
       </c>
       <c r="C12" t="n">
-        <v>647</v>
+        <v>629</v>
       </c>
       <c r="D12" t="n">
-        <v>634</v>
+        <v>668</v>
       </c>
       <c r="E12" t="n">
-        <v>671</v>
+        <v>655</v>
       </c>
       <c r="F12" t="n">
-        <v>633</v>
+        <v>666</v>
       </c>
       <c r="G12" t="n">
-        <v>693</v>
+        <v>698</v>
       </c>
       <c r="H12" t="n">
-        <v>693</v>
+        <v>699</v>
       </c>
       <c r="I12" t="n">
-        <v>657</v>
+        <v>632</v>
       </c>
       <c r="J12" t="n">
-        <v>689</v>
+        <v>672</v>
       </c>
       <c r="K12" t="n">
-        <v>655</v>
+        <v>650</v>
       </c>
       <c r="L12" t="n">
-        <v>660.9</v>
+        <v>662.9</v>
       </c>
     </row>
     <row r="13">
@@ -889,37 +889,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
+        <v>714</v>
+      </c>
+      <c r="C13" t="n">
+        <v>795</v>
+      </c>
+      <c r="D13" t="n">
+        <v>749</v>
+      </c>
+      <c r="E13" t="n">
+        <v>777</v>
+      </c>
+      <c r="F13" t="n">
+        <v>688</v>
+      </c>
+      <c r="G13" t="n">
+        <v>768</v>
+      </c>
+      <c r="H13" t="n">
+        <v>795</v>
+      </c>
+      <c r="I13" t="n">
+        <v>773</v>
+      </c>
+      <c r="J13" t="n">
+        <v>741</v>
+      </c>
+      <c r="K13" t="n">
+        <v>650</v>
+      </c>
+      <c r="L13" t="n">
         <v>745</v>
-      </c>
-      <c r="C13" t="n">
-        <v>828</v>
-      </c>
-      <c r="D13" t="n">
-        <v>771</v>
-      </c>
-      <c r="E13" t="n">
-        <v>762</v>
-      </c>
-      <c r="F13" t="n">
-        <v>731</v>
-      </c>
-      <c r="G13" t="n">
-        <v>763</v>
-      </c>
-      <c r="H13" t="n">
-        <v>891</v>
-      </c>
-      <c r="I13" t="n">
-        <v>748</v>
-      </c>
-      <c r="J13" t="n">
-        <v>821</v>
-      </c>
-      <c r="K13" t="n">
-        <v>785</v>
-      </c>
-      <c r="L13" t="n">
-        <v>784.5</v>
       </c>
     </row>
     <row r="14">
@@ -927,37 +927,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>707</v>
+        <v>625</v>
       </c>
       <c r="C14" t="n">
-        <v>602</v>
+        <v>655</v>
       </c>
       <c r="D14" t="n">
-        <v>558</v>
+        <v>710</v>
       </c>
       <c r="E14" t="n">
-        <v>740</v>
+        <v>628</v>
       </c>
       <c r="F14" t="n">
-        <v>661</v>
+        <v>685</v>
       </c>
       <c r="G14" t="n">
-        <v>763</v>
+        <v>668</v>
       </c>
       <c r="H14" t="n">
-        <v>643</v>
+        <v>775</v>
       </c>
       <c r="I14" t="n">
-        <v>685</v>
+        <v>630</v>
       </c>
       <c r="J14" t="n">
-        <v>709</v>
+        <v>780</v>
       </c>
       <c r="K14" t="n">
-        <v>811</v>
+        <v>702</v>
       </c>
       <c r="L14" t="n">
-        <v>687.9</v>
+        <v>685.8</v>
       </c>
     </row>
     <row r="15">
@@ -965,37 +965,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>722</v>
+        <v>575</v>
       </c>
       <c r="C15" t="n">
-        <v>752</v>
+        <v>626</v>
       </c>
       <c r="D15" t="n">
-        <v>615</v>
+        <v>695</v>
       </c>
       <c r="E15" t="n">
-        <v>806</v>
+        <v>686</v>
       </c>
       <c r="F15" t="n">
-        <v>691</v>
+        <v>645</v>
       </c>
       <c r="G15" t="n">
-        <v>733</v>
+        <v>757</v>
       </c>
       <c r="H15" t="n">
-        <v>788</v>
+        <v>663</v>
       </c>
       <c r="I15" t="n">
-        <v>632</v>
+        <v>684</v>
       </c>
       <c r="J15" t="n">
-        <v>696</v>
+        <v>634</v>
       </c>
       <c r="K15" t="n">
-        <v>683</v>
+        <v>608</v>
       </c>
       <c r="L15" t="n">
-        <v>711.8</v>
+        <v>657.3</v>
       </c>
     </row>
     <row r="16">
@@ -1003,37 +1003,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>672</v>
+        <v>696</v>
       </c>
       <c r="C16" t="n">
+        <v>694</v>
+      </c>
+      <c r="D16" t="n">
+        <v>635</v>
+      </c>
+      <c r="E16" t="n">
+        <v>622</v>
+      </c>
+      <c r="F16" t="n">
+        <v>625</v>
+      </c>
+      <c r="G16" t="n">
         <v>654</v>
       </c>
-      <c r="D16" t="n">
-        <v>644</v>
-      </c>
-      <c r="E16" t="n">
-        <v>671</v>
-      </c>
-      <c r="F16" t="n">
-        <v>694</v>
-      </c>
-      <c r="G16" t="n">
-        <v>634</v>
-      </c>
       <c r="H16" t="n">
+        <v>725</v>
+      </c>
+      <c r="I16" t="n">
+        <v>627</v>
+      </c>
+      <c r="J16" t="n">
         <v>684</v>
       </c>
-      <c r="I16" t="n">
-        <v>652</v>
-      </c>
-      <c r="J16" t="n">
-        <v>654</v>
-      </c>
       <c r="K16" t="n">
-        <v>636</v>
+        <v>685</v>
       </c>
       <c r="L16" t="n">
-        <v>659.5</v>
+        <v>664.7</v>
       </c>
     </row>
     <row r="17">
@@ -1041,37 +1041,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>617</v>
+        <v>607</v>
       </c>
       <c r="C17" t="n">
-        <v>631</v>
+        <v>677</v>
       </c>
       <c r="D17" t="n">
-        <v>699</v>
+        <v>606</v>
       </c>
       <c r="E17" t="n">
-        <v>632</v>
+        <v>748</v>
       </c>
       <c r="F17" t="n">
-        <v>790</v>
+        <v>603</v>
       </c>
       <c r="G17" t="n">
-        <v>717</v>
+        <v>565</v>
       </c>
       <c r="H17" t="n">
-        <v>584</v>
+        <v>621</v>
       </c>
       <c r="I17" t="n">
-        <v>733</v>
+        <v>625</v>
       </c>
       <c r="J17" t="n">
-        <v>701</v>
+        <v>656</v>
       </c>
       <c r="K17" t="n">
-        <v>621</v>
+        <v>580</v>
       </c>
       <c r="L17" t="n">
-        <v>672.5</v>
+        <v>628.8</v>
       </c>
     </row>
     <row r="18">
@@ -1079,37 +1079,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>789</v>
+        <v>712</v>
       </c>
       <c r="C18" t="n">
+        <v>640</v>
+      </c>
+      <c r="D18" t="n">
         <v>708</v>
       </c>
-      <c r="D18" t="n">
-        <v>660</v>
-      </c>
       <c r="E18" t="n">
-        <v>640</v>
+        <v>700</v>
       </c>
       <c r="F18" t="n">
-        <v>762</v>
+        <v>650</v>
       </c>
       <c r="G18" t="n">
-        <v>610</v>
+        <v>726</v>
       </c>
       <c r="H18" t="n">
-        <v>833</v>
+        <v>714</v>
       </c>
       <c r="I18" t="n">
-        <v>619</v>
+        <v>744</v>
       </c>
       <c r="J18" t="n">
-        <v>760</v>
+        <v>694</v>
       </c>
       <c r="K18" t="n">
-        <v>561</v>
+        <v>687</v>
       </c>
       <c r="L18" t="n">
-        <v>694.2</v>
+        <v>697.5</v>
       </c>
     </row>
     <row r="19">
@@ -1117,37 +1117,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>838</v>
+        <v>699</v>
       </c>
       <c r="C19" t="n">
-        <v>641</v>
+        <v>722</v>
       </c>
       <c r="D19" t="n">
-        <v>690</v>
+        <v>713</v>
       </c>
       <c r="E19" t="n">
-        <v>690</v>
+        <v>656</v>
       </c>
       <c r="F19" t="n">
-        <v>602</v>
+        <v>586</v>
       </c>
       <c r="G19" t="n">
-        <v>764</v>
+        <v>631</v>
       </c>
       <c r="H19" t="n">
-        <v>774</v>
+        <v>711</v>
       </c>
       <c r="I19" t="n">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="J19" t="n">
-        <v>668</v>
+        <v>709</v>
       </c>
       <c r="K19" t="n">
-        <v>634</v>
+        <v>612</v>
       </c>
       <c r="L19" t="n">
-        <v>698.6</v>
+        <v>672.6</v>
       </c>
     </row>
     <row r="20">
@@ -1155,37 +1155,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>793</v>
+        <v>822</v>
       </c>
       <c r="C20" t="n">
-        <v>796</v>
+        <v>677</v>
       </c>
       <c r="D20" t="n">
-        <v>873</v>
+        <v>766</v>
       </c>
       <c r="E20" t="n">
-        <v>835</v>
+        <v>782</v>
       </c>
       <c r="F20" t="n">
-        <v>825</v>
+        <v>667</v>
       </c>
       <c r="G20" t="n">
-        <v>705</v>
+        <v>691</v>
       </c>
       <c r="H20" t="n">
-        <v>772</v>
+        <v>728</v>
       </c>
       <c r="I20" t="n">
-        <v>772</v>
+        <v>750</v>
       </c>
       <c r="J20" t="n">
-        <v>773</v>
+        <v>786</v>
       </c>
       <c r="K20" t="n">
-        <v>791</v>
+        <v>706</v>
       </c>
       <c r="L20" t="n">
-        <v>793.5</v>
+        <v>737.5</v>
       </c>
     </row>
     <row r="21">
@@ -1193,37 +1193,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>642</v>
+        <v>731</v>
       </c>
       <c r="C21" t="n">
-        <v>712</v>
+        <v>703</v>
       </c>
       <c r="D21" t="n">
-        <v>680</v>
+        <v>685</v>
       </c>
       <c r="E21" t="n">
-        <v>657</v>
+        <v>700</v>
       </c>
       <c r="F21" t="n">
-        <v>718</v>
+        <v>789</v>
       </c>
       <c r="G21" t="n">
-        <v>683</v>
+        <v>679</v>
       </c>
       <c r="H21" t="n">
-        <v>729</v>
+        <v>638</v>
       </c>
       <c r="I21" t="n">
-        <v>755</v>
+        <v>593</v>
       </c>
       <c r="J21" t="n">
-        <v>619</v>
+        <v>787</v>
       </c>
       <c r="K21" t="n">
-        <v>732</v>
+        <v>695</v>
       </c>
       <c r="L21" t="n">
-        <v>692.7</v>
+        <v>700</v>
       </c>
     </row>
     <row r="22">
@@ -1231,37 +1231,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>594</v>
+        <v>662</v>
       </c>
       <c r="C22" t="n">
-        <v>609</v>
+        <v>643</v>
       </c>
       <c r="D22" t="n">
-        <v>687</v>
+        <v>600</v>
       </c>
       <c r="E22" t="n">
-        <v>742</v>
+        <v>821</v>
       </c>
       <c r="F22" t="n">
-        <v>644</v>
+        <v>749</v>
       </c>
       <c r="G22" t="n">
-        <v>645</v>
+        <v>727</v>
       </c>
       <c r="H22" t="n">
-        <v>678</v>
+        <v>599</v>
       </c>
       <c r="I22" t="n">
-        <v>688</v>
+        <v>671</v>
       </c>
       <c r="J22" t="n">
-        <v>710</v>
+        <v>725</v>
       </c>
       <c r="K22" t="n">
-        <v>641</v>
+        <v>752</v>
       </c>
       <c r="L22" t="n">
-        <v>663.8</v>
+        <v>694.9</v>
       </c>
     </row>
     <row r="23">
@@ -1269,37 +1269,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>703</v>
+        <v>636</v>
       </c>
       <c r="C23" t="n">
-        <v>614</v>
+        <v>681</v>
       </c>
       <c r="D23" t="n">
-        <v>672</v>
+        <v>696</v>
       </c>
       <c r="E23" t="n">
-        <v>577</v>
+        <v>625</v>
       </c>
       <c r="F23" t="n">
-        <v>653</v>
+        <v>602</v>
       </c>
       <c r="G23" t="n">
-        <v>555</v>
+        <v>586</v>
       </c>
       <c r="H23" t="n">
-        <v>598</v>
+        <v>626</v>
       </c>
       <c r="I23" t="n">
-        <v>644</v>
+        <v>586</v>
       </c>
       <c r="J23" t="n">
-        <v>628</v>
+        <v>620</v>
       </c>
       <c r="K23" t="n">
         <v>643</v>
       </c>
       <c r="L23" t="n">
-        <v>628.7</v>
+        <v>630.1</v>
       </c>
     </row>
     <row r="24">
@@ -1307,37 +1307,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>636</v>
+        <v>761</v>
       </c>
       <c r="C24" t="n">
-        <v>578</v>
+        <v>841</v>
       </c>
       <c r="D24" t="n">
-        <v>618</v>
+        <v>867</v>
       </c>
       <c r="E24" t="n">
-        <v>758</v>
+        <v>703</v>
       </c>
       <c r="F24" t="n">
-        <v>640</v>
+        <v>658</v>
       </c>
       <c r="G24" t="n">
-        <v>693</v>
+        <v>688</v>
       </c>
       <c r="H24" t="n">
-        <v>604</v>
+        <v>894</v>
       </c>
       <c r="I24" t="n">
-        <v>716</v>
+        <v>648</v>
       </c>
       <c r="J24" t="n">
-        <v>705</v>
+        <v>655</v>
       </c>
       <c r="K24" t="n">
-        <v>688</v>
+        <v>664</v>
       </c>
       <c r="L24" t="n">
-        <v>663.6</v>
+        <v>737.9</v>
       </c>
     </row>
     <row r="25">
@@ -1345,37 +1345,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>663</v>
+        <v>715</v>
       </c>
       <c r="C25" t="n">
-        <v>645</v>
+        <v>681</v>
       </c>
       <c r="D25" t="n">
-        <v>655</v>
+        <v>610</v>
       </c>
       <c r="E25" t="n">
-        <v>771</v>
+        <v>709</v>
       </c>
       <c r="F25" t="n">
-        <v>593</v>
+        <v>689</v>
       </c>
       <c r="G25" t="n">
-        <v>652</v>
+        <v>639</v>
       </c>
       <c r="H25" t="n">
-        <v>710</v>
+        <v>764</v>
       </c>
       <c r="I25" t="n">
-        <v>654</v>
+        <v>669</v>
       </c>
       <c r="J25" t="n">
-        <v>665</v>
+        <v>626</v>
       </c>
       <c r="K25" t="n">
-        <v>758</v>
+        <v>700</v>
       </c>
       <c r="L25" t="n">
-        <v>676.6</v>
+        <v>680.2</v>
       </c>
     </row>
     <row r="26">
@@ -1383,37 +1383,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>721</v>
+        <v>683</v>
       </c>
       <c r="C26" t="n">
-        <v>751</v>
+        <v>704</v>
       </c>
       <c r="D26" t="n">
-        <v>696</v>
+        <v>766</v>
       </c>
       <c r="E26" t="n">
-        <v>704</v>
+        <v>683</v>
       </c>
       <c r="F26" t="n">
-        <v>735</v>
+        <v>663</v>
       </c>
       <c r="G26" t="n">
-        <v>661</v>
+        <v>671</v>
       </c>
       <c r="H26" t="n">
-        <v>625</v>
+        <v>685</v>
       </c>
       <c r="I26" t="n">
-        <v>678</v>
+        <v>744</v>
       </c>
       <c r="J26" t="n">
-        <v>697</v>
+        <v>634</v>
       </c>
       <c r="K26" t="n">
-        <v>743</v>
+        <v>694</v>
       </c>
       <c r="L26" t="n">
-        <v>701.1</v>
+        <v>692.7</v>
       </c>
     </row>
     <row r="27">
@@ -1421,37 +1421,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>617</v>
+        <v>610</v>
       </c>
       <c r="C27" t="n">
-        <v>549</v>
+        <v>588</v>
       </c>
       <c r="D27" t="n">
-        <v>556</v>
+        <v>645</v>
       </c>
       <c r="E27" t="n">
-        <v>549</v>
+        <v>595</v>
       </c>
       <c r="F27" t="n">
-        <v>578</v>
+        <v>596</v>
       </c>
       <c r="G27" t="n">
-        <v>548</v>
+        <v>623</v>
       </c>
       <c r="H27" t="n">
+        <v>537</v>
+      </c>
+      <c r="I27" t="n">
+        <v>662</v>
+      </c>
+      <c r="J27" t="n">
+        <v>568</v>
+      </c>
+      <c r="K27" t="n">
         <v>529</v>
       </c>
-      <c r="I27" t="n">
-        <v>631</v>
-      </c>
-      <c r="J27" t="n">
-        <v>586</v>
-      </c>
-      <c r="K27" t="n">
-        <v>585</v>
-      </c>
       <c r="L27" t="n">
-        <v>572.8</v>
+        <v>595.3</v>
       </c>
     </row>
     <row r="28">
@@ -1459,37 +1459,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
+        <v>598</v>
+      </c>
+      <c r="C28" t="n">
         <v>619</v>
       </c>
-      <c r="C28" t="n">
-        <v>642</v>
-      </c>
       <c r="D28" t="n">
-        <v>611</v>
+        <v>571</v>
       </c>
       <c r="E28" t="n">
-        <v>588</v>
+        <v>632</v>
       </c>
       <c r="F28" t="n">
-        <v>662</v>
+        <v>623</v>
       </c>
       <c r="G28" t="n">
-        <v>656</v>
+        <v>614</v>
       </c>
       <c r="H28" t="n">
-        <v>669</v>
+        <v>603</v>
       </c>
       <c r="I28" t="n">
-        <v>745</v>
+        <v>643</v>
       </c>
       <c r="J28" t="n">
-        <v>683</v>
+        <v>595</v>
       </c>
       <c r="K28" t="n">
-        <v>611</v>
+        <v>643</v>
       </c>
       <c r="L28" t="n">
-        <v>648.6</v>
+        <v>614.1</v>
       </c>
     </row>
     <row r="29">
@@ -1497,37 +1497,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>626</v>
+        <v>674</v>
       </c>
       <c r="C29" t="n">
-        <v>730</v>
+        <v>652</v>
       </c>
       <c r="D29" t="n">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="E29" t="n">
-        <v>696</v>
+        <v>643</v>
       </c>
       <c r="F29" t="n">
-        <v>614</v>
+        <v>655</v>
       </c>
       <c r="G29" t="n">
-        <v>690</v>
+        <v>646</v>
       </c>
       <c r="H29" t="n">
-        <v>689</v>
+        <v>653</v>
       </c>
       <c r="I29" t="n">
-        <v>608</v>
+        <v>691</v>
       </c>
       <c r="J29" t="n">
-        <v>832</v>
+        <v>658</v>
       </c>
       <c r="K29" t="n">
-        <v>779</v>
+        <v>630</v>
       </c>
       <c r="L29" t="n">
-        <v>690.5</v>
+        <v>654.7</v>
       </c>
     </row>
     <row r="30">
@@ -1535,37 +1535,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>683</v>
+        <v>655</v>
       </c>
       <c r="C30" t="n">
-        <v>631</v>
+        <v>677</v>
       </c>
       <c r="D30" t="n">
-        <v>595</v>
+        <v>681</v>
       </c>
       <c r="E30" t="n">
-        <v>699</v>
+        <v>704</v>
       </c>
       <c r="F30" t="n">
-        <v>711</v>
+        <v>701</v>
       </c>
       <c r="G30" t="n">
+        <v>714</v>
+      </c>
+      <c r="H30" t="n">
+        <v>630</v>
+      </c>
+      <c r="I30" t="n">
+        <v>647</v>
+      </c>
+      <c r="J30" t="n">
+        <v>724</v>
+      </c>
+      <c r="K30" t="n">
         <v>679</v>
       </c>
-      <c r="H30" t="n">
-        <v>650</v>
-      </c>
-      <c r="I30" t="n">
-        <v>572</v>
-      </c>
-      <c r="J30" t="n">
-        <v>634</v>
-      </c>
-      <c r="K30" t="n">
-        <v>579</v>
-      </c>
       <c r="L30" t="n">
-        <v>643.3</v>
+        <v>681.2</v>
       </c>
     </row>
     <row r="31">
@@ -1573,37 +1573,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>818</v>
+        <v>735</v>
       </c>
       <c r="C31" t="n">
-        <v>758</v>
+        <v>651</v>
       </c>
       <c r="D31" t="n">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="E31" t="n">
-        <v>845</v>
+        <v>755</v>
       </c>
       <c r="F31" t="n">
-        <v>687</v>
+        <v>776</v>
       </c>
       <c r="G31" t="n">
-        <v>835</v>
+        <v>795</v>
       </c>
       <c r="H31" t="n">
-        <v>770</v>
+        <v>697</v>
       </c>
       <c r="I31" t="n">
-        <v>752</v>
+        <v>755</v>
       </c>
       <c r="J31" t="n">
-        <v>829</v>
+        <v>697</v>
       </c>
       <c r="K31" t="n">
-        <v>702</v>
+        <v>786</v>
       </c>
       <c r="L31" t="n">
-        <v>772.2</v>
+        <v>737.1</v>
       </c>
     </row>
     <row r="32">
@@ -1611,37 +1611,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>740</v>
+        <v>605</v>
       </c>
       <c r="C32" t="n">
-        <v>803</v>
+        <v>718</v>
       </c>
       <c r="D32" t="n">
-        <v>679</v>
+        <v>624</v>
       </c>
       <c r="E32" t="n">
+        <v>699</v>
+      </c>
+      <c r="F32" t="n">
+        <v>702</v>
+      </c>
+      <c r="G32" t="n">
+        <v>667</v>
+      </c>
+      <c r="H32" t="n">
+        <v>674</v>
+      </c>
+      <c r="I32" t="n">
         <v>701</v>
       </c>
-      <c r="F32" t="n">
-        <v>769</v>
-      </c>
-      <c r="G32" t="n">
-        <v>705</v>
-      </c>
-      <c r="H32" t="n">
-        <v>736</v>
-      </c>
-      <c r="I32" t="n">
-        <v>677</v>
-      </c>
       <c r="J32" t="n">
-        <v>731</v>
+        <v>698</v>
       </c>
       <c r="K32" t="n">
-        <v>721</v>
+        <v>754</v>
       </c>
       <c r="L32" t="n">
-        <v>726.2</v>
+        <v>684.2</v>
       </c>
     </row>
     <row r="33">
@@ -1649,37 +1649,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>715</v>
+        <v>723</v>
       </c>
       <c r="C33" t="n">
-        <v>633</v>
+        <v>725</v>
       </c>
       <c r="D33" t="n">
-        <v>630</v>
+        <v>739</v>
       </c>
       <c r="E33" t="n">
-        <v>668</v>
+        <v>748</v>
       </c>
       <c r="F33" t="n">
-        <v>662</v>
+        <v>757</v>
       </c>
       <c r="G33" t="n">
-        <v>569</v>
+        <v>677</v>
       </c>
       <c r="H33" t="n">
-        <v>745</v>
+        <v>713</v>
       </c>
       <c r="I33" t="n">
-        <v>753</v>
+        <v>689</v>
       </c>
       <c r="J33" t="n">
-        <v>680</v>
+        <v>732</v>
       </c>
       <c r="K33" t="n">
-        <v>694</v>
+        <v>672</v>
       </c>
       <c r="L33" t="n">
-        <v>674.9</v>
+        <v>717.5</v>
       </c>
     </row>
     <row r="34">
@@ -1687,37 +1687,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>620</v>
+        <v>668</v>
       </c>
       <c r="C34" t="n">
-        <v>779</v>
+        <v>650</v>
       </c>
       <c r="D34" t="n">
-        <v>715</v>
+        <v>610</v>
       </c>
       <c r="E34" t="n">
-        <v>657</v>
+        <v>611</v>
       </c>
       <c r="F34" t="n">
-        <v>667</v>
+        <v>606</v>
       </c>
       <c r="G34" t="n">
-        <v>720</v>
+        <v>668</v>
       </c>
       <c r="H34" t="n">
-        <v>619</v>
+        <v>675</v>
       </c>
       <c r="I34" t="n">
-        <v>685</v>
+        <v>662</v>
       </c>
       <c r="J34" t="n">
-        <v>689</v>
+        <v>622</v>
       </c>
       <c r="K34" t="n">
-        <v>664</v>
+        <v>644</v>
       </c>
       <c r="L34" t="n">
-        <v>681.5</v>
+        <v>641.6</v>
       </c>
     </row>
     <row r="35">
@@ -1725,37 +1725,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>702</v>
+        <v>593</v>
       </c>
       <c r="C35" t="n">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="D35" t="n">
-        <v>612</v>
+        <v>574</v>
       </c>
       <c r="E35" t="n">
-        <v>610</v>
+        <v>637</v>
       </c>
       <c r="F35" t="n">
-        <v>633</v>
+        <v>613</v>
       </c>
       <c r="G35" t="n">
-        <v>637</v>
+        <v>604</v>
       </c>
       <c r="H35" t="n">
-        <v>596</v>
+        <v>617</v>
       </c>
       <c r="I35" t="n">
-        <v>560</v>
+        <v>522</v>
       </c>
       <c r="J35" t="n">
-        <v>604</v>
+        <v>622</v>
       </c>
       <c r="K35" t="n">
-        <v>626</v>
+        <v>606</v>
       </c>
       <c r="L35" t="n">
-        <v>617</v>
+        <v>597.3</v>
       </c>
     </row>
     <row r="36">
@@ -1763,37 +1763,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>709</v>
+        <v>688</v>
       </c>
       <c r="C36" t="n">
-        <v>682</v>
+        <v>800</v>
       </c>
       <c r="D36" t="n">
-        <v>739</v>
+        <v>664</v>
       </c>
       <c r="E36" t="n">
-        <v>727</v>
+        <v>715</v>
       </c>
       <c r="F36" t="n">
-        <v>630</v>
+        <v>677</v>
       </c>
       <c r="G36" t="n">
-        <v>607</v>
+        <v>650</v>
       </c>
       <c r="H36" t="n">
-        <v>598</v>
+        <v>679</v>
       </c>
       <c r="I36" t="n">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="J36" t="n">
-        <v>596</v>
+        <v>696</v>
       </c>
       <c r="K36" t="n">
-        <v>666</v>
+        <v>700</v>
       </c>
       <c r="L36" t="n">
-        <v>666.7</v>
+        <v>698.5</v>
       </c>
     </row>
     <row r="37">
@@ -1801,37 +1801,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>796</v>
+        <v>648</v>
       </c>
       <c r="C37" t="n">
-        <v>756</v>
+        <v>621</v>
       </c>
       <c r="D37" t="n">
-        <v>703</v>
+        <v>735</v>
       </c>
       <c r="E37" t="n">
-        <v>642</v>
+        <v>699</v>
       </c>
       <c r="F37" t="n">
-        <v>722</v>
+        <v>715</v>
       </c>
       <c r="G37" t="n">
-        <v>658</v>
+        <v>648</v>
       </c>
       <c r="H37" t="n">
-        <v>652</v>
+        <v>640</v>
       </c>
       <c r="I37" t="n">
-        <v>713</v>
+        <v>704</v>
       </c>
       <c r="J37" t="n">
-        <v>645</v>
+        <v>758</v>
       </c>
       <c r="K37" t="n">
-        <v>659</v>
+        <v>747</v>
       </c>
       <c r="L37" t="n">
-        <v>694.6</v>
+        <v>691.5</v>
       </c>
     </row>
     <row r="38">
@@ -1839,37 +1839,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>692</v>
+        <v>701</v>
       </c>
       <c r="C38" t="n">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="D38" t="n">
-        <v>684</v>
+        <v>644</v>
       </c>
       <c r="E38" t="n">
-        <v>639</v>
+        <v>629</v>
       </c>
       <c r="F38" t="n">
-        <v>653</v>
+        <v>673</v>
       </c>
       <c r="G38" t="n">
-        <v>650</v>
+        <v>743</v>
       </c>
       <c r="H38" t="n">
-        <v>715</v>
+        <v>677</v>
       </c>
       <c r="I38" t="n">
-        <v>579</v>
+        <v>618</v>
       </c>
       <c r="J38" t="n">
-        <v>588</v>
+        <v>606</v>
       </c>
       <c r="K38" t="n">
-        <v>658</v>
+        <v>674</v>
       </c>
       <c r="L38" t="n">
-        <v>649</v>
+        <v>659.6</v>
       </c>
     </row>
     <row r="39">
@@ -1877,37 +1877,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>623</v>
+        <v>550</v>
       </c>
       <c r="C39" t="n">
-        <v>678</v>
+        <v>564</v>
       </c>
       <c r="D39" t="n">
-        <v>645</v>
+        <v>592</v>
       </c>
       <c r="E39" t="n">
-        <v>591</v>
+        <v>533</v>
       </c>
       <c r="F39" t="n">
-        <v>567</v>
+        <v>590</v>
       </c>
       <c r="G39" t="n">
-        <v>607</v>
+        <v>557</v>
       </c>
       <c r="H39" t="n">
-        <v>512</v>
+        <v>609</v>
       </c>
       <c r="I39" t="n">
-        <v>683</v>
+        <v>550</v>
       </c>
       <c r="J39" t="n">
-        <v>638</v>
+        <v>569</v>
       </c>
       <c r="K39" t="n">
-        <v>547</v>
+        <v>589</v>
       </c>
       <c r="L39" t="n">
-        <v>609.1</v>
+        <v>570.3</v>
       </c>
     </row>
     <row r="40">
@@ -1915,37 +1915,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>856</v>
+        <v>771</v>
       </c>
       <c r="C40" t="n">
-        <v>755</v>
+        <v>760</v>
       </c>
       <c r="D40" t="n">
-        <v>712</v>
+        <v>654</v>
       </c>
       <c r="E40" t="n">
-        <v>605</v>
+        <v>757</v>
       </c>
       <c r="F40" t="n">
-        <v>731</v>
+        <v>640</v>
       </c>
       <c r="G40" t="n">
-        <v>649</v>
+        <v>805</v>
       </c>
       <c r="H40" t="n">
-        <v>646</v>
+        <v>679</v>
       </c>
       <c r="I40" t="n">
-        <v>702</v>
+        <v>638</v>
       </c>
       <c r="J40" t="n">
-        <v>743</v>
+        <v>653</v>
       </c>
       <c r="K40" t="n">
-        <v>615</v>
+        <v>738</v>
       </c>
       <c r="L40" t="n">
-        <v>701.4</v>
+        <v>709.5</v>
       </c>
     </row>
     <row r="41">
@@ -1953,37 +1953,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="C41" t="n">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="D41" t="n">
-        <v>619</v>
+        <v>658</v>
       </c>
       <c r="E41" t="n">
-        <v>615</v>
+        <v>608</v>
       </c>
       <c r="F41" t="n">
-        <v>684</v>
+        <v>623</v>
       </c>
       <c r="G41" t="n">
-        <v>630</v>
+        <v>648</v>
       </c>
       <c r="H41" t="n">
-        <v>660</v>
+        <v>678</v>
       </c>
       <c r="I41" t="n">
-        <v>665</v>
+        <v>607</v>
       </c>
       <c r="J41" t="n">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="K41" t="n">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="L41" t="n">
-        <v>641.1</v>
+        <v>636.2</v>
       </c>
     </row>
     <row r="42">
@@ -1991,37 +1991,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="C42" t="n">
-        <v>610</v>
+        <v>645</v>
       </c>
       <c r="D42" t="n">
-        <v>683</v>
+        <v>747</v>
       </c>
       <c r="E42" t="n">
-        <v>600</v>
+        <v>682</v>
       </c>
       <c r="F42" t="n">
-        <v>688</v>
+        <v>717</v>
       </c>
       <c r="G42" t="n">
-        <v>644</v>
+        <v>817</v>
       </c>
       <c r="H42" t="n">
-        <v>713</v>
+        <v>676</v>
       </c>
       <c r="I42" t="n">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="J42" t="n">
-        <v>613</v>
+        <v>647</v>
       </c>
       <c r="K42" t="n">
-        <v>685</v>
+        <v>677</v>
       </c>
       <c r="L42" t="n">
-        <v>661.3</v>
+        <v>698.6</v>
       </c>
     </row>
     <row r="43">
@@ -2029,37 +2029,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>712</v>
+        <v>730</v>
       </c>
       <c r="C43" t="n">
-        <v>769</v>
+        <v>789</v>
       </c>
       <c r="D43" t="n">
-        <v>753</v>
+        <v>731</v>
       </c>
       <c r="E43" t="n">
-        <v>695</v>
+        <v>796</v>
       </c>
       <c r="F43" t="n">
-        <v>657</v>
+        <v>742</v>
       </c>
       <c r="G43" t="n">
-        <v>782</v>
+        <v>821</v>
       </c>
       <c r="H43" t="n">
-        <v>685</v>
+        <v>729</v>
       </c>
       <c r="I43" t="n">
-        <v>691</v>
+        <v>705</v>
       </c>
       <c r="J43" t="n">
-        <v>793</v>
+        <v>717</v>
       </c>
       <c r="K43" t="n">
-        <v>736</v>
+        <v>746</v>
       </c>
       <c r="L43" t="n">
-        <v>727.3</v>
+        <v>750.6</v>
       </c>
     </row>
     <row r="44">
@@ -2067,37 +2067,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>625</v>
+        <v>612</v>
       </c>
       <c r="C44" t="n">
+        <v>786</v>
+      </c>
+      <c r="D44" t="n">
+        <v>576</v>
+      </c>
+      <c r="E44" t="n">
         <v>694</v>
       </c>
-      <c r="D44" t="n">
-        <v>631</v>
-      </c>
-      <c r="E44" t="n">
-        <v>582</v>
-      </c>
       <c r="F44" t="n">
-        <v>642</v>
+        <v>613</v>
       </c>
       <c r="G44" t="n">
-        <v>616</v>
+        <v>678</v>
       </c>
       <c r="H44" t="n">
-        <v>703</v>
+        <v>600</v>
       </c>
       <c r="I44" t="n">
-        <v>615</v>
+        <v>623</v>
       </c>
       <c r="J44" t="n">
-        <v>624</v>
+        <v>633</v>
       </c>
       <c r="K44" t="n">
-        <v>618</v>
+        <v>628</v>
       </c>
       <c r="L44" t="n">
-        <v>635</v>
+        <v>644.3</v>
       </c>
     </row>
     <row r="45">
@@ -2105,37 +2105,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>771</v>
+        <v>783</v>
       </c>
       <c r="C45" t="n">
-        <v>755</v>
+        <v>802</v>
       </c>
       <c r="D45" t="n">
-        <v>667</v>
+        <v>765</v>
       </c>
       <c r="E45" t="n">
-        <v>722</v>
+        <v>708</v>
       </c>
       <c r="F45" t="n">
-        <v>687</v>
+        <v>786</v>
       </c>
       <c r="G45" t="n">
-        <v>721</v>
+        <v>843</v>
       </c>
       <c r="H45" t="n">
-        <v>699</v>
+        <v>713</v>
       </c>
       <c r="I45" t="n">
-        <v>733</v>
+        <v>834</v>
       </c>
       <c r="J45" t="n">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="K45" t="n">
-        <v>653</v>
+        <v>735</v>
       </c>
       <c r="L45" t="n">
-        <v>715.2</v>
+        <v>771.4</v>
       </c>
     </row>
     <row r="46">
@@ -2143,37 +2143,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>594</v>
+        <v>681</v>
       </c>
       <c r="C46" t="n">
-        <v>688</v>
+        <v>647</v>
       </c>
       <c r="D46" t="n">
-        <v>597</v>
+        <v>648</v>
       </c>
       <c r="E46" t="n">
-        <v>678</v>
+        <v>695</v>
       </c>
       <c r="F46" t="n">
-        <v>646</v>
+        <v>603</v>
       </c>
       <c r="G46" t="n">
-        <v>688</v>
+        <v>631</v>
       </c>
       <c r="H46" t="n">
-        <v>707</v>
+        <v>669</v>
       </c>
       <c r="I46" t="n">
-        <v>707</v>
+        <v>675</v>
       </c>
       <c r="J46" t="n">
-        <v>699</v>
+        <v>666</v>
       </c>
       <c r="K46" t="n">
-        <v>629</v>
+        <v>665</v>
       </c>
       <c r="L46" t="n">
-        <v>663.3</v>
+        <v>658</v>
       </c>
     </row>
     <row r="47">
@@ -2181,37 +2181,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>541</v>
+        <v>692</v>
       </c>
       <c r="C47" t="n">
-        <v>560</v>
+        <v>567</v>
       </c>
       <c r="D47" t="n">
-        <v>653</v>
+        <v>604</v>
       </c>
       <c r="E47" t="n">
-        <v>610</v>
+        <v>553</v>
       </c>
       <c r="F47" t="n">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="G47" t="n">
-        <v>695</v>
+        <v>680</v>
       </c>
       <c r="H47" t="n">
-        <v>624</v>
+        <v>630</v>
       </c>
       <c r="I47" t="n">
-        <v>686</v>
+        <v>581</v>
       </c>
       <c r="J47" t="n">
-        <v>644</v>
+        <v>654</v>
       </c>
       <c r="K47" t="n">
-        <v>677</v>
+        <v>656</v>
       </c>
       <c r="L47" t="n">
-        <v>636.3</v>
+        <v>629.3</v>
       </c>
     </row>
     <row r="48">
@@ -2219,37 +2219,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>778</v>
+        <v>912</v>
       </c>
       <c r="C48" t="n">
-        <v>767</v>
+        <v>724</v>
       </c>
       <c r="D48" t="n">
-        <v>808</v>
+        <v>768</v>
       </c>
       <c r="E48" t="n">
-        <v>816</v>
+        <v>782</v>
       </c>
       <c r="F48" t="n">
-        <v>780</v>
+        <v>821</v>
       </c>
       <c r="G48" t="n">
-        <v>670</v>
+        <v>785</v>
       </c>
       <c r="H48" t="n">
-        <v>716</v>
+        <v>779</v>
       </c>
       <c r="I48" t="n">
-        <v>725</v>
+        <v>771</v>
       </c>
       <c r="J48" t="n">
-        <v>796</v>
+        <v>752</v>
       </c>
       <c r="K48" t="n">
-        <v>734</v>
+        <v>776</v>
       </c>
       <c r="L48" t="n">
-        <v>759</v>
+        <v>787</v>
       </c>
     </row>
     <row r="49">
@@ -2257,37 +2257,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>708</v>
+        <v>898</v>
       </c>
       <c r="C49" t="n">
-        <v>731</v>
+        <v>692</v>
       </c>
       <c r="D49" t="n">
-        <v>749</v>
+        <v>745</v>
       </c>
       <c r="E49" t="n">
-        <v>672</v>
+        <v>744</v>
       </c>
       <c r="F49" t="n">
-        <v>732</v>
+        <v>852</v>
       </c>
       <c r="G49" t="n">
-        <v>721</v>
+        <v>797</v>
       </c>
       <c r="H49" t="n">
-        <v>557</v>
+        <v>760</v>
       </c>
       <c r="I49" t="n">
-        <v>617</v>
+        <v>690</v>
       </c>
       <c r="J49" t="n">
-        <v>653</v>
+        <v>740</v>
       </c>
       <c r="K49" t="n">
-        <v>839</v>
+        <v>825</v>
       </c>
       <c r="L49" t="n">
-        <v>697.9</v>
+        <v>774.3</v>
       </c>
     </row>
     <row r="50">
@@ -2295,37 +2295,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>666</v>
+        <v>634</v>
       </c>
       <c r="C50" t="n">
-        <v>746</v>
+        <v>715</v>
       </c>
       <c r="D50" t="n">
+        <v>687</v>
+      </c>
+      <c r="E50" t="n">
+        <v>665</v>
+      </c>
+      <c r="F50" t="n">
         <v>678</v>
       </c>
-      <c r="E50" t="n">
-        <v>707</v>
-      </c>
-      <c r="F50" t="n">
-        <v>776</v>
-      </c>
       <c r="G50" t="n">
-        <v>710</v>
+        <v>620</v>
       </c>
       <c r="H50" t="n">
-        <v>723</v>
+        <v>633</v>
       </c>
       <c r="I50" t="n">
-        <v>707</v>
+        <v>670</v>
       </c>
       <c r="J50" t="n">
-        <v>756</v>
+        <v>614</v>
       </c>
       <c r="K50" t="n">
-        <v>773</v>
+        <v>611</v>
       </c>
       <c r="L50" t="n">
-        <v>724.2</v>
+        <v>652.7</v>
       </c>
     </row>
     <row r="51">
@@ -2333,37 +2333,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>596</v>
+        <v>580</v>
       </c>
       <c r="C51" t="n">
-        <v>731</v>
+        <v>574</v>
       </c>
       <c r="D51" t="n">
-        <v>598</v>
+        <v>589</v>
       </c>
       <c r="E51" t="n">
-        <v>640</v>
+        <v>620</v>
       </c>
       <c r="F51" t="n">
-        <v>656</v>
+        <v>597</v>
       </c>
       <c r="G51" t="n">
-        <v>654</v>
+        <v>602</v>
       </c>
       <c r="H51" t="n">
-        <v>623</v>
+        <v>690</v>
       </c>
       <c r="I51" t="n">
-        <v>577</v>
+        <v>561</v>
       </c>
       <c r="J51" t="n">
-        <v>735</v>
+        <v>659</v>
       </c>
       <c r="K51" t="n">
-        <v>666</v>
+        <v>615</v>
       </c>
       <c r="L51" t="n">
-        <v>647.6</v>
+        <v>608.7</v>
       </c>
     </row>
     <row r="52">
@@ -2373,37 +2373,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>680.42</v>
+        <v>672.92</v>
       </c>
       <c r="C52" t="n">
-        <v>674.08</v>
+        <v>672.36</v>
       </c>
       <c r="D52" t="n">
-        <v>661.5</v>
+        <v>671.08</v>
       </c>
       <c r="E52" t="n">
-        <v>673.36</v>
+        <v>679.0599999999999</v>
       </c>
       <c r="F52" t="n">
-        <v>672.62</v>
+        <v>671.46</v>
       </c>
       <c r="G52" t="n">
-        <v>667.3200000000001</v>
+        <v>675.6799999999999</v>
       </c>
       <c r="H52" t="n">
-        <v>671.26</v>
+        <v>671.22</v>
       </c>
       <c r="I52" t="n">
-        <v>674.7</v>
+        <v>661.9400000000001</v>
       </c>
       <c r="J52" t="n">
-        <v>677.96</v>
+        <v>669.26</v>
       </c>
       <c r="K52" t="n">
-        <v>669.08</v>
+        <v>668</v>
       </c>
       <c r="L52" t="n">
-        <v>672.23</v>
+        <v>671.2979999999999</v>
       </c>
     </row>
   </sheetData>
@@ -2462,37 +2462,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>5.107673406600952</v>
+        <v>4.097855806350708</v>
       </c>
       <c r="C2" t="n">
-        <v>4.451324224472046</v>
+        <v>4.592124938964844</v>
       </c>
       <c r="D2" t="n">
-        <v>4.346341371536255</v>
+        <v>3.913316965103149</v>
       </c>
       <c r="E2" t="n">
-        <v>4.026670455932617</v>
+        <v>4.242970943450928</v>
       </c>
       <c r="F2" t="n">
-        <v>4.006969928741455</v>
+        <v>3.933271169662476</v>
       </c>
       <c r="G2" t="n">
-        <v>3.989084959030151</v>
+        <v>4.137736082077026</v>
       </c>
       <c r="H2" t="n">
-        <v>3.970563888549805</v>
+        <v>3.832020044326782</v>
       </c>
       <c r="I2" t="n">
-        <v>3.990819454193115</v>
+        <v>4.007567882537842</v>
       </c>
       <c r="J2" t="n">
-        <v>4.302233457565308</v>
+        <v>3.892399787902832</v>
       </c>
       <c r="K2" t="n">
-        <v>4.327629566192627</v>
+        <v>3.885417699813843</v>
       </c>
       <c r="L2" t="n">
-        <v>4.251931071281433</v>
+        <v>4.053468132019043</v>
       </c>
     </row>
     <row r="3">
@@ -2500,37 +2500,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>4.682065010070801</v>
+        <v>4.376626491546631</v>
       </c>
       <c r="C3" t="n">
-        <v>4.775830268859863</v>
+        <v>4.441457748413086</v>
       </c>
       <c r="D3" t="n">
-        <v>4.389177083969116</v>
+        <v>4.444981575012207</v>
       </c>
       <c r="E3" t="n">
-        <v>4.232483386993408</v>
+        <v>4.264899015426636</v>
       </c>
       <c r="F3" t="n">
-        <v>4.553047895431519</v>
+        <v>4.565123319625854</v>
       </c>
       <c r="G3" t="n">
-        <v>4.483500242233276</v>
+        <v>4.700283765792847</v>
       </c>
       <c r="H3" t="n">
-        <v>5.228875398635864</v>
+        <v>4.4675133228302</v>
       </c>
       <c r="I3" t="n">
-        <v>4.720752954483032</v>
+        <v>4.228312015533447</v>
       </c>
       <c r="J3" t="n">
-        <v>4.675430297851562</v>
+        <v>4.349681854248047</v>
       </c>
       <c r="K3" t="n">
-        <v>4.667862415313721</v>
+        <v>4.338219881057739</v>
       </c>
       <c r="L3" t="n">
-        <v>4.640902495384216</v>
+        <v>4.41770989894867</v>
       </c>
     </row>
     <row r="4">
@@ -2538,37 +2538,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>3.881919145584106</v>
+        <v>3.315861463546753</v>
       </c>
       <c r="C4" t="n">
-        <v>3.928386211395264</v>
+        <v>3.585668087005615</v>
       </c>
       <c r="D4" t="n">
-        <v>3.842073202133179</v>
+        <v>3.363246202468872</v>
       </c>
       <c r="E4" t="n">
-        <v>4.124103546142578</v>
+        <v>3.755115270614624</v>
       </c>
       <c r="F4" t="n">
-        <v>3.853057146072388</v>
+        <v>3.609823942184448</v>
       </c>
       <c r="G4" t="n">
-        <v>3.61741304397583</v>
+        <v>3.560969352722168</v>
       </c>
       <c r="H4" t="n">
-        <v>3.668908596038818</v>
+        <v>3.492116689682007</v>
       </c>
       <c r="I4" t="n">
-        <v>3.77464485168457</v>
+        <v>3.65620493888855</v>
       </c>
       <c r="J4" t="n">
-        <v>3.592927217483521</v>
+        <v>3.535495758056641</v>
       </c>
       <c r="K4" t="n">
-        <v>3.738897800445557</v>
+        <v>3.547993183135986</v>
       </c>
       <c r="L4" t="n">
-        <v>3.802233076095581</v>
+        <v>3.542249488830566</v>
       </c>
     </row>
     <row r="5">
@@ -2576,37 +2576,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>4.208990097045898</v>
+        <v>4.148934841156006</v>
       </c>
       <c r="C5" t="n">
-        <v>4.204522132873535</v>
+        <v>4.083108186721802</v>
       </c>
       <c r="D5" t="n">
-        <v>4.392522811889648</v>
+        <v>4.04671311378479</v>
       </c>
       <c r="E5" t="n">
-        <v>4.092611789703369</v>
+        <v>4.333494901657104</v>
       </c>
       <c r="F5" t="n">
-        <v>3.866035461425781</v>
+        <v>3.769432067871094</v>
       </c>
       <c r="G5" t="n">
-        <v>4.048274755477905</v>
+        <v>4.34942364692688</v>
       </c>
       <c r="H5" t="n">
-        <v>4.038838148117065</v>
+        <v>4.114039659500122</v>
       </c>
       <c r="I5" t="n">
-        <v>4.222746849060059</v>
+        <v>4.134485960006714</v>
       </c>
       <c r="J5" t="n">
-        <v>3.852094650268555</v>
+        <v>3.816283464431763</v>
       </c>
       <c r="K5" t="n">
-        <v>3.750939130783081</v>
+        <v>4.079597949981689</v>
       </c>
       <c r="L5" t="n">
-        <v>4.067757582664489</v>
+        <v>4.087551379203797</v>
       </c>
     </row>
     <row r="6">
@@ -2614,37 +2614,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>4.496870994567871</v>
+        <v>3.613306522369385</v>
       </c>
       <c r="C6" t="n">
-        <v>3.909938335418701</v>
+        <v>3.501069068908691</v>
       </c>
       <c r="D6" t="n">
-        <v>3.856107950210571</v>
+        <v>3.505879640579224</v>
       </c>
       <c r="E6" t="n">
-        <v>4.170599937438965</v>
+        <v>3.600050926208496</v>
       </c>
       <c r="F6" t="n">
-        <v>4.016032218933105</v>
+        <v>3.817275762557983</v>
       </c>
       <c r="G6" t="n">
-        <v>4.257889747619629</v>
+        <v>3.524028062820435</v>
       </c>
       <c r="H6" t="n">
-        <v>4.004387855529785</v>
+        <v>3.781873941421509</v>
       </c>
       <c r="I6" t="n">
-        <v>4.219137907028198</v>
+        <v>3.615788698196411</v>
       </c>
       <c r="J6" t="n">
-        <v>3.89384913444519</v>
+        <v>3.629274129867554</v>
       </c>
       <c r="K6" t="n">
-        <v>4.237457513809204</v>
+        <v>3.620787143707275</v>
       </c>
       <c r="L6" t="n">
-        <v>4.106227159500122</v>
+        <v>3.620933389663696</v>
       </c>
     </row>
     <row r="7">
@@ -2652,37 +2652,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>3.784097194671631</v>
+        <v>4.11700701713562</v>
       </c>
       <c r="C7" t="n">
-        <v>3.8695228099823</v>
+        <v>3.865657806396484</v>
       </c>
       <c r="D7" t="n">
-        <v>4.2785964012146</v>
+        <v>3.701563358306885</v>
       </c>
       <c r="E7" t="n">
-        <v>4.127018213272095</v>
+        <v>3.786371946334839</v>
       </c>
       <c r="F7" t="n">
-        <v>4.068332672119141</v>
+        <v>3.878635168075562</v>
       </c>
       <c r="G7" t="n">
-        <v>3.99414849281311</v>
+        <v>3.694114923477173</v>
       </c>
       <c r="H7" t="n">
-        <v>3.678094625473022</v>
+        <v>3.896580696105957</v>
       </c>
       <c r="I7" t="n">
-        <v>3.658593654632568</v>
+        <v>3.814295768737793</v>
       </c>
       <c r="J7" t="n">
-        <v>3.860245943069458</v>
+        <v>4.546952247619629</v>
       </c>
       <c r="K7" t="n">
-        <v>3.804560899734497</v>
+        <v>3.774864435195923</v>
       </c>
       <c r="L7" t="n">
-        <v>3.912321090698242</v>
+        <v>3.907604336738586</v>
       </c>
     </row>
     <row r="8">
@@ -2690,37 +2690,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>4.901272535324097</v>
+        <v>4.029522180557251</v>
       </c>
       <c r="C8" t="n">
-        <v>4.309954643249512</v>
+        <v>3.965726613998413</v>
       </c>
       <c r="D8" t="n">
-        <v>4.408589363098145</v>
+        <v>4.338233232498169</v>
       </c>
       <c r="E8" t="n">
-        <v>4.518591642379761</v>
+        <v>4.298314571380615</v>
       </c>
       <c r="F8" t="n">
-        <v>4.33216118812561</v>
+        <v>3.928312540054321</v>
       </c>
       <c r="G8" t="n">
-        <v>4.610877275466919</v>
+        <v>3.930267810821533</v>
       </c>
       <c r="H8" t="n">
-        <v>4.270309209823608</v>
+        <v>3.819058895111084</v>
       </c>
       <c r="I8" t="n">
-        <v>4.145287036895752</v>
+        <v>4.124781847000122</v>
       </c>
       <c r="J8" t="n">
-        <v>4.024005174636841</v>
+        <v>4.301319360733032</v>
       </c>
       <c r="K8" t="n">
-        <v>4.357485055923462</v>
+        <v>4.046442747116089</v>
       </c>
       <c r="L8" t="n">
-        <v>4.38785331249237</v>
+        <v>4.078197979927063</v>
       </c>
     </row>
     <row r="9">
@@ -2728,37 +2728,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>3.801851987838745</v>
+        <v>3.421282768249512</v>
       </c>
       <c r="C9" t="n">
-        <v>3.936266660690308</v>
+        <v>3.817286252975464</v>
       </c>
       <c r="D9" t="n">
-        <v>3.693681716918945</v>
+        <v>3.384401559829712</v>
       </c>
       <c r="E9" t="n">
-        <v>3.770996809005737</v>
+        <v>3.509580612182617</v>
       </c>
       <c r="F9" t="n">
-        <v>3.599145889282227</v>
+        <v>3.73299765586853</v>
       </c>
       <c r="G9" t="n">
-        <v>3.846406221389771</v>
+        <v>3.595832347869873</v>
       </c>
       <c r="H9" t="n">
-        <v>3.776837587356567</v>
+        <v>3.910562753677368</v>
       </c>
       <c r="I9" t="n">
-        <v>3.709030389785767</v>
+        <v>4.007818937301636</v>
       </c>
       <c r="J9" t="n">
-        <v>3.84658408164978</v>
+        <v>4.954931020736694</v>
       </c>
       <c r="K9" t="n">
-        <v>4.950373411178589</v>
+        <v>4.228796005249023</v>
       </c>
       <c r="L9" t="n">
-        <v>3.893117475509643</v>
+        <v>3.856348991394043</v>
       </c>
     </row>
     <row r="10">
@@ -2766,37 +2766,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>4.926333427429199</v>
+        <v>6.702844858169556</v>
       </c>
       <c r="C10" t="n">
-        <v>5.095853090286255</v>
+        <v>5.757895946502686</v>
       </c>
       <c r="D10" t="n">
-        <v>5.199996709823608</v>
+        <v>5.435194730758667</v>
       </c>
       <c r="E10" t="n">
-        <v>5.131517171859741</v>
+        <v>5.810276508331299</v>
       </c>
       <c r="F10" t="n">
-        <v>5.035023212432861</v>
+        <v>5.678120851516724</v>
       </c>
       <c r="G10" t="n">
-        <v>5.153841972351074</v>
+        <v>5.232746601104736</v>
       </c>
       <c r="H10" t="n">
-        <v>4.771193265914917</v>
+        <v>4.901475667953491</v>
       </c>
       <c r="I10" t="n">
-        <v>4.798578500747681</v>
+        <v>5.049132347106934</v>
       </c>
       <c r="J10" t="n">
-        <v>5.005725145339966</v>
+        <v>4.919027328491211</v>
       </c>
       <c r="K10" t="n">
-        <v>5.169427394866943</v>
+        <v>4.892030954360962</v>
       </c>
       <c r="L10" t="n">
-        <v>5.028748989105225</v>
+        <v>5.437874579429627</v>
       </c>
     </row>
     <row r="11">
@@ -2804,37 +2804,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>4.226177215576172</v>
+        <v>4.254681825637817</v>
       </c>
       <c r="C11" t="n">
-        <v>4.5958251953125</v>
+        <v>4.771370887756348</v>
       </c>
       <c r="D11" t="n">
-        <v>5.289824485778809</v>
+        <v>4.512525081634521</v>
       </c>
       <c r="E11" t="n">
-        <v>4.662141799926758</v>
+        <v>4.475616931915283</v>
       </c>
       <c r="F11" t="n">
-        <v>4.655574083328247</v>
+        <v>4.572349071502686</v>
       </c>
       <c r="G11" t="n">
-        <v>4.471137523651123</v>
+        <v>4.379334211349487</v>
       </c>
       <c r="H11" t="n">
-        <v>4.851274490356445</v>
+        <v>4.603705406188965</v>
       </c>
       <c r="I11" t="n">
-        <v>5.008363962173462</v>
+        <v>4.323009014129639</v>
       </c>
       <c r="J11" t="n">
-        <v>4.446118831634521</v>
+        <v>4.25217604637146</v>
       </c>
       <c r="K11" t="n">
-        <v>4.73852801322937</v>
+        <v>4.53495979309082</v>
       </c>
       <c r="L11" t="n">
-        <v>4.694496560096741</v>
+        <v>4.467972826957703</v>
       </c>
     </row>
     <row r="12">
@@ -2842,37 +2842,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>4.17451286315918</v>
+        <v>3.884609222412109</v>
       </c>
       <c r="C12" t="n">
-        <v>4.021982669830322</v>
+        <v>3.96591329574585</v>
       </c>
       <c r="D12" t="n">
-        <v>4.117619752883911</v>
+        <v>4.104073524475098</v>
       </c>
       <c r="E12" t="n">
-        <v>4.275930643081665</v>
+        <v>3.890117883682251</v>
       </c>
       <c r="F12" t="n">
-        <v>3.971401929855347</v>
+        <v>3.843716144561768</v>
       </c>
       <c r="G12" t="n">
-        <v>4.3250732421875</v>
+        <v>3.948437213897705</v>
       </c>
       <c r="H12" t="n">
-        <v>4.223342657089233</v>
+        <v>3.864665269851685</v>
       </c>
       <c r="I12" t="n">
-        <v>4.832727193832397</v>
+        <v>3.832256555557251</v>
       </c>
       <c r="J12" t="n">
-        <v>4.042012214660645</v>
+        <v>3.817284107208252</v>
       </c>
       <c r="K12" t="n">
-        <v>4.371023416519165</v>
+        <v>3.834231376647949</v>
       </c>
       <c r="L12" t="n">
-        <v>4.235562658309936</v>
+        <v>3.898530459403992</v>
       </c>
     </row>
     <row r="13">
@@ -2880,37 +2880,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>4.766981601715088</v>
+        <v>4.703545093536377</v>
       </c>
       <c r="C13" t="n">
-        <v>4.834032535552979</v>
+        <v>5.441640377044678</v>
       </c>
       <c r="D13" t="n">
-        <v>4.472137928009033</v>
+        <v>4.602754354476929</v>
       </c>
       <c r="E13" t="n">
-        <v>4.97236704826355</v>
+        <v>5.050641298294067</v>
       </c>
       <c r="F13" t="n">
-        <v>4.405487298965454</v>
+        <v>4.436708450317383</v>
       </c>
       <c r="G13" t="n">
-        <v>4.941154003143311</v>
+        <v>4.418730735778809</v>
       </c>
       <c r="H13" t="n">
-        <v>5.468094348907471</v>
+        <v>5.119487285614014</v>
       </c>
       <c r="I13" t="n">
-        <v>4.664474725723267</v>
+        <v>4.673250436782837</v>
       </c>
       <c r="J13" t="n">
-        <v>6.042631149291992</v>
+        <v>4.423732042312622</v>
       </c>
       <c r="K13" t="n">
-        <v>4.924669027328491</v>
+        <v>4.344424486160278</v>
       </c>
       <c r="L13" t="n">
-        <v>4.949202966690064</v>
+        <v>4.721491456031799</v>
       </c>
     </row>
     <row r="14">
@@ -2918,37 +2918,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>4.186843872070312</v>
+        <v>3.913539886474609</v>
       </c>
       <c r="C14" t="n">
-        <v>4.186720371246338</v>
+        <v>4.075112342834473</v>
       </c>
       <c r="D14" t="n">
-        <v>4.011952877044678</v>
+        <v>4.362898826599121</v>
       </c>
       <c r="E14" t="n">
-        <v>4.370835542678833</v>
+        <v>4.01580286026001</v>
       </c>
       <c r="F14" t="n">
-        <v>4.308515071868896</v>
+        <v>3.977355480194092</v>
       </c>
       <c r="G14" t="n">
-        <v>5.100445032119751</v>
+        <v>3.85268497467041</v>
       </c>
       <c r="H14" t="n">
-        <v>3.986648797988892</v>
+        <v>4.914932250976562</v>
       </c>
       <c r="I14" t="n">
-        <v>4.151279449462891</v>
+        <v>4.090858221054077</v>
       </c>
       <c r="J14" t="n">
-        <v>4.365360736846924</v>
+        <v>4.498821020126343</v>
       </c>
       <c r="K14" t="n">
-        <v>4.750030755996704</v>
+        <v>4.309293985366821</v>
       </c>
       <c r="L14" t="n">
-        <v>4.341863250732422</v>
+        <v>4.201129984855652</v>
       </c>
     </row>
     <row r="15">
@@ -2956,37 +2956,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>4.62456226348877</v>
+        <v>4.650956869125366</v>
       </c>
       <c r="C15" t="n">
-        <v>4.828771114349365</v>
+        <v>4.355693817138672</v>
       </c>
       <c r="D15" t="n">
-        <v>4.449266672134399</v>
+        <v>4.494300127029419</v>
       </c>
       <c r="E15" t="n">
-        <v>5.522355318069458</v>
+        <v>4.724794626235962</v>
       </c>
       <c r="F15" t="n">
-        <v>4.808668851852417</v>
+        <v>4.516759157180786</v>
       </c>
       <c r="G15" t="n">
-        <v>4.435648679733276</v>
+        <v>4.576603412628174</v>
       </c>
       <c r="H15" t="n">
-        <v>5.5843505859375</v>
+        <v>4.27240252494812</v>
       </c>
       <c r="I15" t="n">
-        <v>4.542499780654907</v>
+        <v>4.54170298576355</v>
       </c>
       <c r="J15" t="n">
-        <v>4.945159912109375</v>
+        <v>4.069929838180542</v>
       </c>
       <c r="K15" t="n">
-        <v>4.408376216888428</v>
+        <v>4.283401489257812</v>
       </c>
       <c r="L15" t="n">
-        <v>4.814965939521789</v>
+        <v>4.448654484748841</v>
       </c>
     </row>
     <row r="16">
@@ -2994,37 +2994,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>4.689278841018677</v>
+        <v>4.246975898742676</v>
       </c>
       <c r="C16" t="n">
-        <v>4.20672082901001</v>
+        <v>4.24296760559082</v>
       </c>
       <c r="D16" t="n">
-        <v>4.26871132850647</v>
+        <v>4.009569883346558</v>
       </c>
       <c r="E16" t="n">
-        <v>4.440632343292236</v>
+        <v>4.048005104064941</v>
       </c>
       <c r="F16" t="n">
-        <v>4.061150789260864</v>
+        <v>4.039489269256592</v>
       </c>
       <c r="G16" t="n">
-        <v>4.318205595016479</v>
+        <v>4.054989337921143</v>
       </c>
       <c r="H16" t="n">
-        <v>4.676774501800537</v>
+        <v>4.1905837059021</v>
       </c>
       <c r="I16" t="n">
-        <v>4.239996433258057</v>
+        <v>4.083897590637207</v>
       </c>
       <c r="J16" t="n">
-        <v>4.323261976242065</v>
+        <v>3.982628107070923</v>
       </c>
       <c r="K16" t="n">
-        <v>4.022885084152222</v>
+        <v>4.127752065658569</v>
       </c>
       <c r="L16" t="n">
-        <v>4.324761772155762</v>
+        <v>4.102685856819153</v>
       </c>
     </row>
     <row r="17">
@@ -3032,37 +3032,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>4.218538761138916</v>
+        <v>4.155211210250854</v>
       </c>
       <c r="C17" t="n">
-        <v>4.467144012451172</v>
+        <v>4.041501760482788</v>
       </c>
       <c r="D17" t="n">
-        <v>5.466770648956299</v>
+        <v>4.211034536361694</v>
       </c>
       <c r="E17" t="n">
-        <v>4.540483236312866</v>
+        <v>5.002010345458984</v>
       </c>
       <c r="F17" t="n">
-        <v>4.718047142028809</v>
+        <v>4.007576465606689</v>
       </c>
       <c r="G17" t="n">
-        <v>4.264999628067017</v>
+        <v>4.194092512130737</v>
       </c>
       <c r="H17" t="n">
-        <v>4.13036847114563</v>
+        <v>3.955216646194458</v>
       </c>
       <c r="I17" t="n">
-        <v>4.450975894927979</v>
+        <v>3.946738719940186</v>
       </c>
       <c r="J17" t="n">
-        <v>4.482347011566162</v>
+        <v>4.382113218307495</v>
       </c>
       <c r="K17" t="n">
-        <v>4.638720750808716</v>
+        <v>4.100942850112915</v>
       </c>
       <c r="L17" t="n">
-        <v>4.537839555740357</v>
+        <v>4.19964382648468</v>
       </c>
     </row>
     <row r="18">
@@ -3070,37 +3070,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>4.503873348236084</v>
+        <v>4.296604871749878</v>
       </c>
       <c r="C18" t="n">
-        <v>4.503458738327026</v>
+        <v>4.141460657119751</v>
       </c>
       <c r="D18" t="n">
-        <v>4.118187427520752</v>
+        <v>4.743532419204712</v>
       </c>
       <c r="E18" t="n">
-        <v>4.243274211883545</v>
+        <v>4.525769472122192</v>
       </c>
       <c r="F18" t="n">
-        <v>4.905182600021362</v>
+        <v>4.777218103408813</v>
       </c>
       <c r="G18" t="n">
-        <v>4.415752172470093</v>
+        <v>5.143503189086914</v>
       </c>
       <c r="H18" t="n">
-        <v>5.29656195640564</v>
+        <v>4.408454656600952</v>
       </c>
       <c r="I18" t="n">
-        <v>4.538207769393921</v>
+        <v>4.498043298721313</v>
       </c>
       <c r="J18" t="n">
-        <v>5.175346612930298</v>
+        <v>4.283275365829468</v>
       </c>
       <c r="K18" t="n">
-        <v>4.054542779922485</v>
+        <v>4.759636402130127</v>
       </c>
       <c r="L18" t="n">
-        <v>4.575438761711121</v>
+        <v>4.557749843597412</v>
       </c>
     </row>
     <row r="19">
@@ -3108,37 +3108,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>5.043606758117676</v>
+        <v>4.398329734802246</v>
       </c>
       <c r="C19" t="n">
-        <v>4.083603143692017</v>
+        <v>4.554448127746582</v>
       </c>
       <c r="D19" t="n">
-        <v>4.44907021522522</v>
+        <v>4.133345365524292</v>
       </c>
       <c r="E19" t="n">
-        <v>4.287845134735107</v>
+        <v>3.820261478424072</v>
       </c>
       <c r="F19" t="n">
-        <v>4.105465650558472</v>
+        <v>3.928086280822754</v>
       </c>
       <c r="G19" t="n">
-        <v>4.222754716873169</v>
+        <v>4.186142206192017</v>
       </c>
       <c r="H19" t="n">
-        <v>4.856295824050903</v>
+        <v>4.226051330566406</v>
       </c>
       <c r="I19" t="n">
-        <v>4.033395051956177</v>
+        <v>4.163426876068115</v>
       </c>
       <c r="J19" t="n">
-        <v>4.60590386390686</v>
+        <v>4.480131149291992</v>
       </c>
       <c r="K19" t="n">
-        <v>4.350018262863159</v>
+        <v>4.292083024978638</v>
       </c>
       <c r="L19" t="n">
-        <v>4.403795862197876</v>
+        <v>4.218230557441712</v>
       </c>
     </row>
     <row r="20">
@@ -3146,37 +3146,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>5.585995674133301</v>
+        <v>5.112529516220093</v>
       </c>
       <c r="C20" t="n">
-        <v>5.397188663482666</v>
+        <v>4.980227947235107</v>
       </c>
       <c r="D20" t="n">
-        <v>4.657313823699951</v>
+        <v>4.948173761367798</v>
       </c>
       <c r="E20" t="n">
-        <v>5.314490556716919</v>
+        <v>5.461837768554688</v>
       </c>
       <c r="F20" t="n">
-        <v>5.408847332000732</v>
+        <v>5.391024589538574</v>
       </c>
       <c r="G20" t="n">
-        <v>5.444500684738159</v>
+        <v>5.32373046875</v>
       </c>
       <c r="H20" t="n">
-        <v>5.375746011734009</v>
+        <v>4.916735887527466</v>
       </c>
       <c r="I20" t="n">
-        <v>4.71583366394043</v>
+        <v>6.012435913085938</v>
       </c>
       <c r="J20" t="n">
-        <v>5.070721864700317</v>
+        <v>7.216387987136841</v>
       </c>
       <c r="K20" t="n">
-        <v>5.065441131591797</v>
+        <v>7.154072999954224</v>
       </c>
       <c r="L20" t="n">
-        <v>5.203607940673828</v>
+        <v>5.651715683937073</v>
       </c>
     </row>
     <row r="21">
@@ -3184,37 +3184,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>4.462951183319092</v>
+        <v>5.76409125328064</v>
       </c>
       <c r="C21" t="n">
-        <v>4.563050985336304</v>
+        <v>4.049705266952515</v>
       </c>
       <c r="D21" t="n">
-        <v>4.84207010269165</v>
+        <v>4.928964853286743</v>
       </c>
       <c r="E21" t="n">
-        <v>4.271606922149658</v>
+        <v>4.564411163330078</v>
       </c>
       <c r="F21" t="n">
-        <v>4.656208038330078</v>
+        <v>5.01728892326355</v>
       </c>
       <c r="G21" t="n">
-        <v>5.38904333114624</v>
+        <v>5.656720399856567</v>
       </c>
       <c r="H21" t="n">
-        <v>4.417279720306396</v>
+        <v>4.91804051399231</v>
       </c>
       <c r="I21" t="n">
-        <v>4.709333658218384</v>
+        <v>5.209784030914307</v>
       </c>
       <c r="J21" t="n">
-        <v>4.699863195419312</v>
+        <v>5.729981422424316</v>
       </c>
       <c r="K21" t="n">
-        <v>4.505633354187012</v>
+        <v>5.737525939941406</v>
       </c>
       <c r="L21" t="n">
-        <v>4.651704049110412</v>
+        <v>5.157651376724243</v>
       </c>
     </row>
     <row r="22">
@@ -3222,37 +3222,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>4.536317348480225</v>
+        <v>5.661718845367432</v>
       </c>
       <c r="C22" t="n">
-        <v>4.472716331481934</v>
+        <v>6.164213895797729</v>
       </c>
       <c r="D22" t="n">
-        <v>5.206646680831909</v>
+        <v>5.891366481781006</v>
       </c>
       <c r="E22" t="n">
-        <v>4.905590534210205</v>
+        <v>6.091212511062622</v>
       </c>
       <c r="F22" t="n">
-        <v>4.558994770050049</v>
+        <v>6.07825493812561</v>
       </c>
       <c r="G22" t="n">
-        <v>4.738349676132202</v>
+        <v>6.075194597244263</v>
       </c>
       <c r="H22" t="n">
-        <v>5.074280261993408</v>
+        <v>5.163094282150269</v>
       </c>
       <c r="I22" t="n">
-        <v>4.54869818687439</v>
+        <v>4.74448037147522</v>
       </c>
       <c r="J22" t="n">
-        <v>4.509629726409912</v>
+        <v>4.637877702713013</v>
       </c>
       <c r="K22" t="n">
-        <v>4.720975637435913</v>
+        <v>4.582370042800903</v>
       </c>
       <c r="L22" t="n">
-        <v>4.727219915390014</v>
+        <v>5.508978366851807</v>
       </c>
     </row>
     <row r="23">
@@ -3260,37 +3260,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>4.62685489654541</v>
+        <v>4.337463617324829</v>
       </c>
       <c r="C23" t="n">
-        <v>4.527883052825928</v>
+        <v>4.037764310836792</v>
       </c>
       <c r="D23" t="n">
-        <v>4.38331413269043</v>
+        <v>4.541483879089355</v>
       </c>
       <c r="E23" t="n">
-        <v>4.085438966751099</v>
+        <v>4.287081718444824</v>
       </c>
       <c r="F23" t="n">
-        <v>4.233687877655029</v>
+        <v>4.265681743621826</v>
       </c>
       <c r="G23" t="n">
-        <v>4.14306378364563</v>
+        <v>5.176931858062744</v>
       </c>
       <c r="H23" t="n">
-        <v>4.029397964477539</v>
+        <v>4.950885057449341</v>
       </c>
       <c r="I23" t="n">
-        <v>4.292737245559692</v>
+        <v>4.155697822570801</v>
       </c>
       <c r="J23" t="n">
-        <v>4.307058572769165</v>
+        <v>4.157208204269409</v>
       </c>
       <c r="K23" t="n">
-        <v>4.234814405441284</v>
+        <v>4.45846700668335</v>
       </c>
       <c r="L23" t="n">
-        <v>4.28642508983612</v>
+        <v>4.436866521835327</v>
       </c>
     </row>
     <row r="24">
@@ -3298,37 +3298,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>4.195849895477295</v>
+        <v>4.902252912521362</v>
       </c>
       <c r="C24" t="n">
-        <v>4.468261241912842</v>
+        <v>5.266985177993774</v>
       </c>
       <c r="D24" t="n">
-        <v>4.935356140136719</v>
+        <v>5.386992216110229</v>
       </c>
       <c r="E24" t="n">
-        <v>4.799908399581909</v>
+        <v>4.341236591339111</v>
       </c>
       <c r="F24" t="n">
-        <v>4.444687366485596</v>
+        <v>4.2988440990448</v>
       </c>
       <c r="G24" t="n">
-        <v>4.357296943664551</v>
+        <v>4.863154888153076</v>
       </c>
       <c r="H24" t="n">
-        <v>4.543220281600952</v>
+        <v>5.643662691116333</v>
       </c>
       <c r="I24" t="n">
-        <v>4.846493244171143</v>
+        <v>4.585366725921631</v>
       </c>
       <c r="J24" t="n">
-        <v>4.566025257110596</v>
+        <v>4.64120626449585</v>
       </c>
       <c r="K24" t="n">
-        <v>4.368453979492188</v>
+        <v>4.726171255111694</v>
       </c>
       <c r="L24" t="n">
-        <v>4.552555274963379</v>
+        <v>4.865587282180786</v>
       </c>
     </row>
     <row r="25">
@@ -3336,37 +3336,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>4.294136524200439</v>
+        <v>4.338473796844482</v>
       </c>
       <c r="C25" t="n">
-        <v>4.509227752685547</v>
+        <v>5.307065486907959</v>
       </c>
       <c r="D25" t="n">
-        <v>4.17853856086731</v>
+        <v>4.211308240890503</v>
       </c>
       <c r="E25" t="n">
-        <v>4.875578165054321</v>
+        <v>4.921004295349121</v>
       </c>
       <c r="F25" t="n">
-        <v>4.313275575637817</v>
+        <v>4.117549419403076</v>
       </c>
       <c r="G25" t="n">
-        <v>4.180001497268677</v>
+        <v>4.232208967208862</v>
       </c>
       <c r="H25" t="n">
-        <v>4.531109094619751</v>
+        <v>4.554540634155273</v>
       </c>
       <c r="I25" t="n">
-        <v>4.608899831771851</v>
+        <v>4.116031169891357</v>
       </c>
       <c r="J25" t="n">
-        <v>4.115829467773438</v>
+        <v>4.222622156143188</v>
       </c>
       <c r="K25" t="n">
-        <v>4.357110738754272</v>
+        <v>4.862880945205688</v>
       </c>
       <c r="L25" t="n">
-        <v>4.396370720863342</v>
+        <v>4.488368511199951</v>
       </c>
     </row>
     <row r="26">
@@ -3374,37 +3374,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>4.509363651275635</v>
+        <v>4.344737529754639</v>
       </c>
       <c r="C26" t="n">
-        <v>4.528683662414551</v>
+        <v>4.535763025283813</v>
       </c>
       <c r="D26" t="n">
-        <v>4.635990381240845</v>
+        <v>4.784084320068359</v>
       </c>
       <c r="E26" t="n">
-        <v>4.595995426177979</v>
+        <v>4.545707225799561</v>
       </c>
       <c r="F26" t="n">
-        <v>4.861676692962646</v>
+        <v>4.380663633346558</v>
       </c>
       <c r="G26" t="n">
-        <v>4.592740774154663</v>
+        <v>4.468401432037354</v>
       </c>
       <c r="H26" t="n">
-        <v>4.535929441452026</v>
+        <v>4.585086822509766</v>
       </c>
       <c r="I26" t="n">
-        <v>4.45486044883728</v>
+        <v>4.536692380905151</v>
       </c>
       <c r="J26" t="n">
-        <v>4.281953811645508</v>
+        <v>4.405556201934814</v>
       </c>
       <c r="K26" t="n">
-        <v>4.653117418289185</v>
+        <v>4.486844062805176</v>
       </c>
       <c r="L26" t="n">
-        <v>4.565031170845032</v>
+        <v>4.507353663444519</v>
       </c>
     </row>
     <row r="27">
@@ -3412,37 +3412,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>4.132872819900513</v>
+        <v>3.908344507217407</v>
       </c>
       <c r="C27" t="n">
-        <v>3.662834405899048</v>
+        <v>4.178138017654419</v>
       </c>
       <c r="D27" t="n">
-        <v>3.88958740234375</v>
+        <v>4.282367944717407</v>
       </c>
       <c r="E27" t="n">
-        <v>4.191238641738892</v>
+        <v>4.164689779281616</v>
       </c>
       <c r="F27" t="n">
-        <v>3.943825721740723</v>
+        <v>4.106830835342407</v>
       </c>
       <c r="G27" t="n">
-        <v>3.799636363983154</v>
+        <v>3.801178693771362</v>
       </c>
       <c r="H27" t="n">
-        <v>4.038806438446045</v>
+        <v>3.857488870620728</v>
       </c>
       <c r="I27" t="n">
-        <v>3.794561862945557</v>
+        <v>4.600090265274048</v>
       </c>
       <c r="J27" t="n">
-        <v>3.900831937789917</v>
+        <v>4.227066516876221</v>
       </c>
       <c r="K27" t="n">
-        <v>3.802289247512817</v>
+        <v>3.894109487533569</v>
       </c>
       <c r="L27" t="n">
-        <v>3.915648484230041</v>
+        <v>4.102030491828918</v>
       </c>
     </row>
     <row r="28">
@@ -3450,37 +3450,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>4.123876571655273</v>
+        <v>3.971195697784424</v>
       </c>
       <c r="C28" t="n">
-        <v>4.046358585357666</v>
+        <v>4.006279945373535</v>
       </c>
       <c r="D28" t="n">
-        <v>4.140695571899414</v>
+        <v>4.312606573104858</v>
       </c>
       <c r="E28" t="n">
-        <v>3.849400520324707</v>
+        <v>4.526556015014648</v>
       </c>
       <c r="F28" t="n">
-        <v>4.26906681060791</v>
+        <v>3.934491634368896</v>
       </c>
       <c r="G28" t="n">
-        <v>4.682426691055298</v>
+        <v>3.953453302383423</v>
       </c>
       <c r="H28" t="n">
-        <v>4.551072120666504</v>
+        <v>4.247577905654907</v>
       </c>
       <c r="I28" t="n">
-        <v>4.562903165817261</v>
+        <v>4.265845775604248</v>
       </c>
       <c r="J28" t="n">
-        <v>4.43299412727356</v>
+        <v>4.27997350692749</v>
       </c>
       <c r="K28" t="n">
-        <v>4.019763469696045</v>
+        <v>4.0185546875</v>
       </c>
       <c r="L28" t="n">
-        <v>4.267855763435364</v>
+        <v>4.151653504371643</v>
       </c>
     </row>
     <row r="29">
@@ -3488,37 +3488,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>4.314166307449341</v>
+        <v>4.253437995910645</v>
       </c>
       <c r="C29" t="n">
-        <v>4.202017784118652</v>
+        <v>4.015543937683105</v>
       </c>
       <c r="D29" t="n">
-        <v>4.392363309860229</v>
+        <v>4.004593372344971</v>
       </c>
       <c r="E29" t="n">
-        <v>4.962688684463501</v>
+        <v>4.465419054031372</v>
       </c>
       <c r="F29" t="n">
-        <v>3.938601016998291</v>
+        <v>4.177206993103027</v>
       </c>
       <c r="G29" t="n">
-        <v>4.178637027740479</v>
+        <v>4.137767314910889</v>
       </c>
       <c r="H29" t="n">
-        <v>3.977927684783936</v>
+        <v>4.018762826919556</v>
       </c>
       <c r="I29" t="n">
-        <v>4.167570114135742</v>
+        <v>4.274642467498779</v>
       </c>
       <c r="J29" t="n">
-        <v>4.591621398925781</v>
+        <v>4.343470335006714</v>
       </c>
       <c r="K29" t="n">
-        <v>4.609034776687622</v>
+        <v>4.108664512634277</v>
       </c>
       <c r="L29" t="n">
-        <v>4.333462810516357</v>
+        <v>4.179950881004333</v>
       </c>
     </row>
     <row r="30">
@@ -3526,37 +3526,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>4.345832586288452</v>
+        <v>4.328487396240234</v>
       </c>
       <c r="C30" t="n">
-        <v>4.238483905792236</v>
+        <v>4.507355213165283</v>
       </c>
       <c r="D30" t="n">
-        <v>4.543986558914185</v>
+        <v>4.506078958511353</v>
       </c>
       <c r="E30" t="n">
-        <v>4.641669034957886</v>
+        <v>4.223238229751587</v>
       </c>
       <c r="F30" t="n">
-        <v>4.706091642379761</v>
+        <v>4.001819133758545</v>
       </c>
       <c r="G30" t="n">
-        <v>4.355579614639282</v>
+        <v>4.430581092834473</v>
       </c>
       <c r="H30" t="n">
-        <v>4.557083129882812</v>
+        <v>4.150969505310059</v>
       </c>
       <c r="I30" t="n">
-        <v>4.452306270599365</v>
+        <v>5.322904109954834</v>
       </c>
       <c r="J30" t="n">
-        <v>4.500455617904663</v>
+        <v>4.612300395965576</v>
       </c>
       <c r="K30" t="n">
-        <v>4.202175617218018</v>
+        <v>4.367401361465454</v>
       </c>
       <c r="L30" t="n">
-        <v>4.454366397857666</v>
+        <v>4.44511353969574</v>
       </c>
     </row>
     <row r="31">
@@ -3564,37 +3564,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>4.866287469863892</v>
+        <v>4.893081426620483</v>
       </c>
       <c r="C31" t="n">
-        <v>5.118046045303345</v>
+        <v>4.80900764465332</v>
       </c>
       <c r="D31" t="n">
-        <v>4.630811214447021</v>
+        <v>4.938971281051636</v>
       </c>
       <c r="E31" t="n">
-        <v>5.350605010986328</v>
+        <v>5.389458656311035</v>
       </c>
       <c r="F31" t="n">
-        <v>4.963444232940674</v>
+        <v>5.038932323455811</v>
       </c>
       <c r="G31" t="n">
-        <v>5.336973905563354</v>
+        <v>4.977056503295898</v>
       </c>
       <c r="H31" t="n">
-        <v>4.945305109024048</v>
+        <v>4.575143098831177</v>
       </c>
       <c r="I31" t="n">
-        <v>4.646737098693848</v>
+        <v>5.106235504150391</v>
       </c>
       <c r="J31" t="n">
-        <v>4.673956394195557</v>
+        <v>5.024942874908447</v>
       </c>
       <c r="K31" t="n">
-        <v>4.835651636123657</v>
+        <v>5.167077541351318</v>
       </c>
       <c r="L31" t="n">
-        <v>4.936781811714172</v>
+        <v>4.991990685462952</v>
       </c>
     </row>
     <row r="32">
@@ -3602,37 +3602,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>4.93998384475708</v>
+        <v>4.398888111114502</v>
       </c>
       <c r="C32" t="n">
-        <v>5.233891248703003</v>
+        <v>4.301563262939453</v>
       </c>
       <c r="D32" t="n">
-        <v>4.424133539199829</v>
+        <v>4.362892150878906</v>
       </c>
       <c r="E32" t="n">
-        <v>4.725601196289062</v>
+        <v>4.633304834365845</v>
       </c>
       <c r="F32" t="n">
-        <v>5.553151369094849</v>
+        <v>4.484860420227051</v>
       </c>
       <c r="G32" t="n">
-        <v>4.890544414520264</v>
+        <v>4.417507886886597</v>
       </c>
       <c r="H32" t="n">
-        <v>4.8316969871521</v>
+        <v>4.627677202224731</v>
       </c>
       <c r="I32" t="n">
-        <v>4.46179986000061</v>
+        <v>4.720231056213379</v>
       </c>
       <c r="J32" t="n">
-        <v>5.388284683227539</v>
+        <v>4.442546367645264</v>
       </c>
       <c r="K32" t="n">
-        <v>5.814414262771606</v>
+        <v>4.465709209442139</v>
       </c>
       <c r="L32" t="n">
-        <v>5.026350140571594</v>
+        <v>4.485518050193787</v>
       </c>
     </row>
     <row r="33">
@@ -3640,37 +3640,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>4.283146381378174</v>
+        <v>5.091285943984985</v>
       </c>
       <c r="C33" t="n">
-        <v>4.444928884506226</v>
+        <v>5.185590505599976</v>
       </c>
       <c r="D33" t="n">
-        <v>4.859989643096924</v>
+        <v>4.766140699386597</v>
       </c>
       <c r="E33" t="n">
-        <v>4.521362781524658</v>
+        <v>4.628790616989136</v>
       </c>
       <c r="F33" t="n">
-        <v>4.120747566223145</v>
+        <v>5.089273691177368</v>
       </c>
       <c r="G33" t="n">
-        <v>4.250184297561646</v>
+        <v>4.526750564575195</v>
       </c>
       <c r="H33" t="n">
-        <v>4.506769895553589</v>
+        <v>4.34052038192749</v>
       </c>
       <c r="I33" t="n">
-        <v>5.10191798210144</v>
+        <v>4.751321315765381</v>
       </c>
       <c r="J33" t="n">
-        <v>4.647288084030151</v>
+        <v>5.48073410987854</v>
       </c>
       <c r="K33" t="n">
-        <v>4.60621166229248</v>
+        <v>4.502079248428345</v>
       </c>
       <c r="L33" t="n">
-        <v>4.534254717826843</v>
+        <v>4.836248707771301</v>
       </c>
     </row>
     <row r="34">
@@ -3678,37 +3678,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>4.183196306228638</v>
+        <v>4.672002553939819</v>
       </c>
       <c r="C34" t="n">
-        <v>4.341926336288452</v>
+        <v>3.702071905136108</v>
       </c>
       <c r="D34" t="n">
-        <v>3.788317680358887</v>
+        <v>3.941013336181641</v>
       </c>
       <c r="E34" t="n">
-        <v>4.017581939697266</v>
+        <v>3.999956607818604</v>
       </c>
       <c r="F34" t="n">
-        <v>3.842571020126343</v>
+        <v>3.737797260284424</v>
       </c>
       <c r="G34" t="n">
-        <v>4.1238112449646</v>
+        <v>3.704550504684448</v>
       </c>
       <c r="H34" t="n">
-        <v>4.065998077392578</v>
+        <v>4.190123319625854</v>
       </c>
       <c r="I34" t="n">
-        <v>3.870681047439575</v>
+        <v>4.296141862869263</v>
       </c>
       <c r="J34" t="n">
-        <v>3.792453050613403</v>
+        <v>3.993761539459229</v>
       </c>
       <c r="K34" t="n">
-        <v>3.682301044464111</v>
+        <v>3.781388282775879</v>
       </c>
       <c r="L34" t="n">
-        <v>3.970883774757385</v>
+        <v>4.001880717277527</v>
       </c>
     </row>
     <row r="35">
@@ -3716,37 +3716,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>4.059326648712158</v>
+        <v>3.94746208190918</v>
       </c>
       <c r="C35" t="n">
-        <v>3.695977210998535</v>
+        <v>3.647207260131836</v>
       </c>
       <c r="D35" t="n">
-        <v>3.991510629653931</v>
+        <v>3.701061010360718</v>
       </c>
       <c r="E35" t="n">
-        <v>3.6529221534729</v>
+        <v>3.990845680236816</v>
       </c>
       <c r="F35" t="n">
-        <v>3.886187791824341</v>
+        <v>4.230289459228516</v>
       </c>
       <c r="G35" t="n">
-        <v>4.475119113922119</v>
+        <v>4.252930641174316</v>
       </c>
       <c r="H35" t="n">
-        <v>3.717511653900146</v>
+        <v>3.937773704528809</v>
       </c>
       <c r="I35" t="n">
-        <v>3.607397079467773</v>
+        <v>3.694373607635498</v>
       </c>
       <c r="J35" t="n">
-        <v>3.672443389892578</v>
+        <v>4.068148136138916</v>
       </c>
       <c r="K35" t="n">
-        <v>3.642485857009888</v>
+        <v>3.989831209182739</v>
       </c>
       <c r="L35" t="n">
-        <v>3.840088152885437</v>
+        <v>3.945992279052734</v>
       </c>
     </row>
     <row r="36">
@@ -3754,37 +3754,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>4.638948917388916</v>
+        <v>4.033745765686035</v>
       </c>
       <c r="C36" t="n">
-        <v>4.284018039703369</v>
+        <v>4.906053066253662</v>
       </c>
       <c r="D36" t="n">
-        <v>4.345392465591431</v>
+        <v>4.261669874191284</v>
       </c>
       <c r="E36" t="n">
-        <v>4.436151027679443</v>
+        <v>4.408813953399658</v>
       </c>
       <c r="F36" t="n">
-        <v>4.19243597984314</v>
+        <v>4.022764921188354</v>
       </c>
       <c r="G36" t="n">
-        <v>3.98626184463501</v>
+        <v>4.156970500946045</v>
       </c>
       <c r="H36" t="n">
-        <v>4.387811899185181</v>
+        <v>4.206817865371704</v>
       </c>
       <c r="I36" t="n">
-        <v>4.694833517074585</v>
+        <v>3.954941511154175</v>
       </c>
       <c r="J36" t="n">
-        <v>4.373427867889404</v>
+        <v>4.145936489105225</v>
       </c>
       <c r="K36" t="n">
-        <v>4.325979232788086</v>
+        <v>3.932494878768921</v>
       </c>
       <c r="L36" t="n">
-        <v>4.366526079177857</v>
+        <v>4.203020882606507</v>
       </c>
     </row>
     <row r="37">
@@ -3792,37 +3792,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>5.248899459838867</v>
+        <v>4.935442447662354</v>
       </c>
       <c r="C37" t="n">
-        <v>4.954864978790283</v>
+        <v>4.748407602310181</v>
       </c>
       <c r="D37" t="n">
-        <v>4.670810461044312</v>
+        <v>5.252615213394165</v>
       </c>
       <c r="E37" t="n">
-        <v>5.160401344299316</v>
+        <v>5.075369834899902</v>
       </c>
       <c r="F37" t="n">
-        <v>4.78730845451355</v>
+        <v>5.12448525428772</v>
       </c>
       <c r="G37" t="n">
-        <v>5.087627172470093</v>
+        <v>5.302035808563232</v>
       </c>
       <c r="H37" t="n">
-        <v>4.825795888900757</v>
+        <v>4.58957052230835</v>
       </c>
       <c r="I37" t="n">
-        <v>4.895625352859497</v>
+        <v>5.164099931716919</v>
       </c>
       <c r="J37" t="n">
-        <v>4.957894563674927</v>
+        <v>5.098262548446655</v>
       </c>
       <c r="K37" t="n">
-        <v>4.854522228240967</v>
+        <v>5.213896751403809</v>
       </c>
       <c r="L37" t="n">
-        <v>4.944374990463257</v>
+        <v>5.050418591499328</v>
       </c>
     </row>
     <row r="38">
@@ -3830,37 +3830,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>4.213606834411621</v>
+        <v>4.027082920074463</v>
       </c>
       <c r="C38" t="n">
-        <v>3.935699939727783</v>
+        <v>4.643382549285889</v>
       </c>
       <c r="D38" t="n">
-        <v>3.913315534591675</v>
+        <v>3.969013690948486</v>
       </c>
       <c r="E38" t="n">
-        <v>3.941228151321411</v>
+        <v>4.155618190765381</v>
       </c>
       <c r="F38" t="n">
-        <v>3.935789346694946</v>
+        <v>4.381617546081543</v>
       </c>
       <c r="G38" t="n">
-        <v>3.983501672744751</v>
+        <v>4.153952836990356</v>
       </c>
       <c r="H38" t="n">
-        <v>3.82679009437561</v>
+        <v>4.234226942062378</v>
       </c>
       <c r="I38" t="n">
-        <v>3.962675333023071</v>
+        <v>4.614301919937134</v>
       </c>
       <c r="J38" t="n">
-        <v>3.733523607254028</v>
+        <v>4.403835535049438</v>
       </c>
       <c r="K38" t="n">
-        <v>3.91349196434021</v>
+        <v>4.057982206344604</v>
       </c>
       <c r="L38" t="n">
-        <v>3.935962247848511</v>
+        <v>4.264101433753967</v>
       </c>
     </row>
     <row r="39">
@@ -3868,37 +3868,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>4.500823736190796</v>
+        <v>3.96502685546875</v>
       </c>
       <c r="C39" t="n">
-        <v>4.410967826843262</v>
+        <v>4.020275831222534</v>
       </c>
       <c r="D39" t="n">
-        <v>4.318986177444458</v>
+        <v>4.240208387374878</v>
       </c>
       <c r="E39" t="n">
-        <v>4.682222604751587</v>
+        <v>3.988751173019409</v>
       </c>
       <c r="F39" t="n">
-        <v>4.210229396820068</v>
+        <v>4.01979660987854</v>
       </c>
       <c r="G39" t="n">
-        <v>4.196242332458496</v>
+        <v>4.120039939880371</v>
       </c>
       <c r="H39" t="n">
-        <v>3.941480875015259</v>
+        <v>4.006815433502197</v>
       </c>
       <c r="I39" t="n">
-        <v>4.186753511428833</v>
+        <v>3.941383361816406</v>
       </c>
       <c r="J39" t="n">
-        <v>4.412806510925293</v>
+        <v>4.145502328872681</v>
       </c>
       <c r="K39" t="n">
-        <v>3.987194061279297</v>
+        <v>4.006678104400635</v>
       </c>
       <c r="L39" t="n">
-        <v>4.284770703315735</v>
+        <v>4.04544780254364</v>
       </c>
     </row>
     <row r="40">
@@ -3906,37 +3906,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>5.444999694824219</v>
+        <v>5.28626537322998</v>
       </c>
       <c r="C40" t="n">
-        <v>5.183216094970703</v>
+        <v>5.164618015289307</v>
       </c>
       <c r="D40" t="n">
-        <v>4.783572435379028</v>
+        <v>4.471118927001953</v>
       </c>
       <c r="E40" t="n">
-        <v>4.517759323120117</v>
+        <v>4.864665985107422</v>
       </c>
       <c r="F40" t="n">
-        <v>4.604335308074951</v>
+        <v>4.467184543609619</v>
       </c>
       <c r="G40" t="n">
-        <v>4.562807559967041</v>
+        <v>5.402270555496216</v>
       </c>
       <c r="H40" t="n">
-        <v>5.051130056381226</v>
+        <v>5.034251928329468</v>
       </c>
       <c r="I40" t="n">
-        <v>4.85938549041748</v>
+        <v>4.599329948425293</v>
       </c>
       <c r="J40" t="n">
-        <v>4.737802505493164</v>
+        <v>4.842778444290161</v>
       </c>
       <c r="K40" t="n">
-        <v>4.384373664855957</v>
+        <v>5.183834314346313</v>
       </c>
       <c r="L40" t="n">
-        <v>4.812938213348389</v>
+        <v>4.931631803512573</v>
       </c>
     </row>
     <row r="41">
@@ -3944,37 +3944,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>4.000874519348145</v>
+        <v>4.123015403747559</v>
       </c>
       <c r="C41" t="n">
-        <v>4.174307584762573</v>
+        <v>4.559429407119751</v>
       </c>
       <c r="D41" t="n">
-        <v>4.480138301849365</v>
+        <v>4.080627679824829</v>
       </c>
       <c r="E41" t="n">
-        <v>4.077230215072632</v>
+        <v>4.020779371261597</v>
       </c>
       <c r="F41" t="n">
-        <v>4.680856943130493</v>
+        <v>4.581390380859375</v>
       </c>
       <c r="G41" t="n">
-        <v>4.102728843688965</v>
+        <v>4.283626556396484</v>
       </c>
       <c r="H41" t="n">
-        <v>4.296036243438721</v>
+        <v>4.401826858520508</v>
       </c>
       <c r="I41" t="n">
-        <v>4.589887380599976</v>
+        <v>4.079617261886597</v>
       </c>
       <c r="J41" t="n">
-        <v>4.472038745880127</v>
+        <v>3.979939222335815</v>
       </c>
       <c r="K41" t="n">
-        <v>4.405973434448242</v>
+        <v>4.071226119995117</v>
       </c>
       <c r="L41" t="n">
-        <v>4.328007221221924</v>
+        <v>4.218147826194763</v>
       </c>
     </row>
     <row r="42">
@@ -3982,37 +3982,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>5.116697072982788</v>
+        <v>4.63196849822998</v>
       </c>
       <c r="C42" t="n">
-        <v>4.289892435073853</v>
+        <v>4.345210075378418</v>
       </c>
       <c r="D42" t="n">
-        <v>4.695135593414307</v>
+        <v>4.495343685150146</v>
       </c>
       <c r="E42" t="n">
-        <v>4.684227705001831</v>
+        <v>4.387599945068359</v>
       </c>
       <c r="F42" t="n">
-        <v>4.697520017623901</v>
+        <v>4.543429613113403</v>
       </c>
       <c r="G42" t="n">
-        <v>4.857490301132202</v>
+        <v>4.932954072952271</v>
       </c>
       <c r="H42" t="n">
-        <v>4.585150241851807</v>
+        <v>4.836704254150391</v>
       </c>
       <c r="I42" t="n">
-        <v>4.75452995300293</v>
+        <v>4.559895038604736</v>
       </c>
       <c r="J42" t="n">
-        <v>4.410445690155029</v>
+        <v>4.716035127639771</v>
       </c>
       <c r="K42" t="n">
-        <v>5.25322699546814</v>
+        <v>4.539942026138306</v>
       </c>
       <c r="L42" t="n">
-        <v>4.734431600570678</v>
+        <v>4.598908233642578</v>
       </c>
     </row>
     <row r="43">
@@ -4020,37 +4020,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>4.309398174285889</v>
+        <v>4.752905368804932</v>
       </c>
       <c r="C43" t="n">
-        <v>4.916476011276245</v>
+        <v>5.172313928604126</v>
       </c>
       <c r="D43" t="n">
-        <v>5.252642869949341</v>
+        <v>4.623242855072021</v>
       </c>
       <c r="E43" t="n">
-        <v>4.942918539047241</v>
+        <v>4.606273651123047</v>
       </c>
       <c r="F43" t="n">
-        <v>4.344280004501343</v>
+        <v>4.960387468338013</v>
       </c>
       <c r="G43" t="n">
-        <v>4.691803693771362</v>
+        <v>4.419741630554199</v>
       </c>
       <c r="H43" t="n">
-        <v>4.489794254302979</v>
+        <v>4.593070983886719</v>
       </c>
       <c r="I43" t="n">
-        <v>4.432842254638672</v>
+        <v>4.244189500808716</v>
       </c>
       <c r="J43" t="n">
-        <v>4.676323652267456</v>
+        <v>4.951400756835938</v>
       </c>
       <c r="K43" t="n">
-        <v>4.730305194854736</v>
+        <v>4.712651491165161</v>
       </c>
       <c r="L43" t="n">
-        <v>4.678678464889527</v>
+        <v>4.703617763519287</v>
       </c>
     </row>
     <row r="44">
@@ -4058,37 +4058,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>4.566627979278564</v>
+        <v>4.242989063262939</v>
       </c>
       <c r="C44" t="n">
-        <v>4.534771919250488</v>
+        <v>5.200103282928467</v>
       </c>
       <c r="D44" t="n">
-        <v>4.260486841201782</v>
+        <v>4.044036626815796</v>
       </c>
       <c r="E44" t="n">
-        <v>4.501737594604492</v>
+        <v>4.046471357345581</v>
       </c>
       <c r="F44" t="n">
-        <v>4.618511199951172</v>
+        <v>4.079898834228516</v>
       </c>
       <c r="G44" t="n">
-        <v>4.445901870727539</v>
+        <v>4.255388021469116</v>
       </c>
       <c r="H44" t="n">
-        <v>4.723281383514404</v>
+        <v>4.418812274932861</v>
       </c>
       <c r="I44" t="n">
-        <v>4.366362333297729</v>
+        <v>4.153467416763306</v>
       </c>
       <c r="J44" t="n">
-        <v>4.374040126800537</v>
+        <v>4.230216264724731</v>
       </c>
       <c r="K44" t="n">
-        <v>4.633857727050781</v>
+        <v>4.093425512313843</v>
       </c>
       <c r="L44" t="n">
-        <v>4.502557897567749</v>
+        <v>4.276480865478516</v>
       </c>
     </row>
     <row r="45">
@@ -4096,37 +4096,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>4.638034343719482</v>
+        <v>4.163670301437378</v>
       </c>
       <c r="C45" t="n">
-        <v>3.739264011383057</v>
+        <v>4.323768138885498</v>
       </c>
       <c r="D45" t="n">
-        <v>4.004884958267212</v>
+        <v>4.3392333984375</v>
       </c>
       <c r="E45" t="n">
-        <v>4.0712571144104</v>
+        <v>3.890383005142212</v>
       </c>
       <c r="F45" t="n">
-        <v>4.384023904800415</v>
+        <v>4.313387155532837</v>
       </c>
       <c r="G45" t="n">
-        <v>4.562548398971558</v>
+        <v>5.056853055953979</v>
       </c>
       <c r="H45" t="n">
-        <v>4.294764518737793</v>
+        <v>4.087021589279175</v>
       </c>
       <c r="I45" t="n">
-        <v>3.962039232254028</v>
+        <v>4.406776905059814</v>
       </c>
       <c r="J45" t="n">
-        <v>4.108566761016846</v>
+        <v>3.992841243743896</v>
       </c>
       <c r="K45" t="n">
-        <v>3.963898897171021</v>
+        <v>4.38214373588562</v>
       </c>
       <c r="L45" t="n">
-        <v>4.172928214073181</v>
+        <v>4.295607852935791</v>
       </c>
     </row>
     <row r="46">
@@ -4134,37 +4134,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>4.25336480140686</v>
+        <v>4.205303907394409</v>
       </c>
       <c r="C46" t="n">
-        <v>4.98044490814209</v>
+        <v>4.366877317428589</v>
       </c>
       <c r="D46" t="n">
-        <v>4.32410192489624</v>
+        <v>4.683354616165161</v>
       </c>
       <c r="E46" t="n">
-        <v>4.567404985427856</v>
+        <v>4.600075721740723</v>
       </c>
       <c r="F46" t="n">
-        <v>4.337687492370605</v>
+        <v>4.347257375717163</v>
       </c>
       <c r="G46" t="n">
-        <v>4.619745016098022</v>
+        <v>4.466355085372925</v>
       </c>
       <c r="H46" t="n">
-        <v>4.829648494720459</v>
+        <v>4.535946369171143</v>
       </c>
       <c r="I46" t="n">
-        <v>5.024161577224731</v>
+        <v>4.491784572601318</v>
       </c>
       <c r="J46" t="n">
-        <v>4.809343099594116</v>
+        <v>4.783872842788696</v>
       </c>
       <c r="K46" t="n">
-        <v>4.149678707122803</v>
+        <v>4.085594177246094</v>
       </c>
       <c r="L46" t="n">
-        <v>4.589558100700378</v>
+        <v>4.456642198562622</v>
       </c>
     </row>
     <row r="47">
@@ -4172,37 +4172,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>3.992179870605469</v>
+        <v>3.752924919128418</v>
       </c>
       <c r="C47" t="n">
-        <v>3.935430765151978</v>
+        <v>3.7761549949646</v>
       </c>
       <c r="D47" t="n">
-        <v>4.175249814987183</v>
+        <v>3.730004072189331</v>
       </c>
       <c r="E47" t="n">
-        <v>4.221497535705566</v>
+        <v>3.513542413711548</v>
       </c>
       <c r="F47" t="n">
-        <v>3.683961391448975</v>
+        <v>3.760307550430298</v>
       </c>
       <c r="G47" t="n">
-        <v>3.992618322372437</v>
+        <v>3.878654718399048</v>
       </c>
       <c r="H47" t="n">
-        <v>4.09471583366394</v>
+        <v>3.853719234466553</v>
       </c>
       <c r="I47" t="n">
-        <v>4.419933319091797</v>
+        <v>3.821277856826782</v>
       </c>
       <c r="J47" t="n">
-        <v>3.923050403594971</v>
+        <v>3.918755531311035</v>
       </c>
       <c r="K47" t="n">
-        <v>4.283113956451416</v>
+        <v>4.640712738037109</v>
       </c>
       <c r="L47" t="n">
-        <v>4.072175121307373</v>
+        <v>3.864605402946472</v>
       </c>
     </row>
     <row r="48">
@@ -4210,37 +4210,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>4.730629920959473</v>
+        <v>5.513248443603516</v>
       </c>
       <c r="C48" t="n">
-        <v>5.198635339736938</v>
+        <v>4.827104091644287</v>
       </c>
       <c r="D48" t="n">
-        <v>5.140497207641602</v>
+        <v>5.467862367630005</v>
       </c>
       <c r="E48" t="n">
-        <v>4.94386887550354</v>
+        <v>4.932684898376465</v>
       </c>
       <c r="F48" t="n">
-        <v>4.492135047912598</v>
+        <v>4.924244403839111</v>
       </c>
       <c r="G48" t="n">
-        <v>4.701456069946289</v>
+        <v>4.835453748703003</v>
       </c>
       <c r="H48" t="n">
-        <v>4.82374119758606</v>
+        <v>4.658931016921997</v>
       </c>
       <c r="I48" t="n">
-        <v>4.672663688659668</v>
+        <v>4.716293811798096</v>
       </c>
       <c r="J48" t="n">
-        <v>4.928725957870483</v>
+        <v>4.719376564025879</v>
       </c>
       <c r="K48" t="n">
-        <v>4.65330171585083</v>
+        <v>4.923777341842651</v>
       </c>
       <c r="L48" t="n">
-        <v>4.828565502166748</v>
+        <v>4.951897668838501</v>
       </c>
     </row>
     <row r="49">
@@ -4248,37 +4248,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>4.365641832351685</v>
+        <v>5.126436710357666</v>
       </c>
       <c r="C49" t="n">
-        <v>4.268419981002808</v>
+        <v>4.019761562347412</v>
       </c>
       <c r="D49" t="n">
-        <v>5.142621278762817</v>
+        <v>5.796296119689941</v>
       </c>
       <c r="E49" t="n">
-        <v>4.494165182113647</v>
+        <v>4.988296031951904</v>
       </c>
       <c r="F49" t="n">
-        <v>5.154625177383423</v>
+        <v>5.11249041557312</v>
       </c>
       <c r="G49" t="n">
-        <v>4.455217838287354</v>
+        <v>4.816761493682861</v>
       </c>
       <c r="H49" t="n">
-        <v>4.210731506347656</v>
+        <v>4.243041515350342</v>
       </c>
       <c r="I49" t="n">
-        <v>3.952004194259644</v>
+        <v>4.732491016387939</v>
       </c>
       <c r="J49" t="n">
-        <v>5.523627042770386</v>
+        <v>5.184856176376343</v>
       </c>
       <c r="K49" t="n">
-        <v>4.432149410247803</v>
+        <v>7.24991774559021</v>
       </c>
       <c r="L49" t="n">
-        <v>4.599920344352722</v>
+        <v>5.127034878730774</v>
       </c>
     </row>
     <row r="50">
@@ -4286,37 +4286,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>4.227513790130615</v>
+        <v>3.909342765808105</v>
       </c>
       <c r="C50" t="n">
-        <v>4.492144346237183</v>
+        <v>4.054032325744629</v>
       </c>
       <c r="D50" t="n">
-        <v>3.967029094696045</v>
+        <v>3.989148855209351</v>
       </c>
       <c r="E50" t="n">
-        <v>4.210318803787231</v>
+        <v>4.80842661857605</v>
       </c>
       <c r="F50" t="n">
-        <v>4.014955282211304</v>
+        <v>3.970911026000977</v>
       </c>
       <c r="G50" t="n">
-        <v>4.052107810974121</v>
+        <v>4.783910751342773</v>
       </c>
       <c r="H50" t="n">
-        <v>4.279976606369019</v>
+        <v>4.147949934005737</v>
       </c>
       <c r="I50" t="n">
-        <v>4.421118974685669</v>
+        <v>3.584869146347046</v>
       </c>
       <c r="J50" t="n">
-        <v>4.699469327926636</v>
+        <v>3.63475775718689</v>
       </c>
       <c r="K50" t="n">
-        <v>4.810988664627075</v>
+        <v>4.118910312652588</v>
       </c>
       <c r="L50" t="n">
-        <v>4.31756227016449</v>
+        <v>4.100225949287415</v>
       </c>
     </row>
     <row r="51">
@@ -4324,37 +4324,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>3.944181442260742</v>
+        <v>3.740490674972534</v>
       </c>
       <c r="C51" t="n">
-        <v>4.33336329460144</v>
+        <v>3.9094398021698</v>
       </c>
       <c r="D51" t="n">
-        <v>4.174413204193115</v>
+        <v>3.814078807830811</v>
       </c>
       <c r="E51" t="n">
-        <v>4.353795051574707</v>
+        <v>3.75673508644104</v>
       </c>
       <c r="F51" t="n">
-        <v>4.382095813751221</v>
+        <v>3.747285842895508</v>
       </c>
       <c r="G51" t="n">
-        <v>4.19879412651062</v>
+        <v>3.921117067337036</v>
       </c>
       <c r="H51" t="n">
-        <v>4.335793495178223</v>
+        <v>4.85350513458252</v>
       </c>
       <c r="I51" t="n">
-        <v>3.960106134414673</v>
+        <v>4.121053695678711</v>
       </c>
       <c r="J51" t="n">
-        <v>4.186550378799438</v>
+        <v>4.273641347885132</v>
       </c>
       <c r="K51" t="n">
-        <v>4.025400638580322</v>
+        <v>4.260227203369141</v>
       </c>
       <c r="L51" t="n">
-        <v>4.18944935798645</v>
+        <v>4.039757466316223</v>
       </c>
     </row>
     <row r="52">
@@ -4364,37 +4364,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>4.477560596466065</v>
+        <v>4.413260183334351</v>
       </c>
       <c r="C52" t="n">
-        <v>4.42586501121521</v>
+        <v>4.438630366325379</v>
       </c>
       <c r="D52" t="n">
-        <v>4.44401062965393</v>
+        <v>4.401470375061035</v>
       </c>
       <c r="E52" t="n">
-        <v>4.481566424369812</v>
+        <v>4.428666653633118</v>
       </c>
       <c r="F52" t="n">
-        <v>4.389822292327881</v>
+        <v>4.354397978782654</v>
       </c>
       <c r="G52" t="n">
-        <v>4.438627390861511</v>
+        <v>4.445282506942749</v>
       </c>
       <c r="H52" t="n">
-        <v>4.463549933433533</v>
+        <v>4.383020706176758</v>
       </c>
       <c r="I52" t="n">
-        <v>4.393983297348022</v>
+        <v>4.367392387390137</v>
       </c>
       <c r="J52" t="n">
-        <v>4.459205684661865</v>
+        <v>4.452824954986572</v>
       </c>
       <c r="K52" t="n">
-        <v>4.42381516456604</v>
+        <v>4.455548758506775</v>
       </c>
       <c r="L52" t="n">
-        <v>4.439800642490387</v>
+        <v>4.414049487113953</v>
       </c>
     </row>
   </sheetData>
